--- a/sources/BANQUE_OFFICIELLE_CSP.xlsx
+++ b/sources/BANQUE_OFFICIELLE_CSP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Documents\GitHub\Chatbot_civique2\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BF3D67-CA3D-4695-A8F2-8B943210E598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0752135-A356-4AEF-81B9-93CA34C34755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Banque_CSP_191" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="2015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="2016">
   <si>
     <t>ID</t>
   </si>
@@ -2303,9 +2303,6 @@
   </si>
   <si>
     <t>La Déclaration universelle des droits de l'homme de 1948.</t>
-  </si>
-  <si>
-    <t>La Convention européenne des droits de l'homme.</t>
   </si>
   <si>
     <t>Adoptée pendant la Révolution française, la DDHC affirme notamment la liberté, l'égalité devant la loi et les principaux droits des citoyens.</t>
@@ -6078,6 +6075,12 @@
   </si>
   <si>
     <t>Les services d'urgence sont destinés à prendre en charge les situations graves nécessitant des soins immédiats.</t>
+  </si>
+  <si>
+    <t>Le Code civil de 1804</t>
+  </si>
+  <si>
+    <t>La Convention européenne des droits de l'homme de 1908.</t>
   </si>
 </sst>
 </file>
@@ -7024,16 +7027,16 @@
         <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>29</v>
@@ -7042,7 +7045,7 @@
         <v>30</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>31</v>
@@ -7113,7 +7116,7 @@
         <v>46</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>47</v>
@@ -7243,10 +7246,10 @@
         <v>66</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>29</v>
@@ -7255,7 +7258,7 @@
         <v>69</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>31</v>
@@ -7308,7 +7311,7 @@
         <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>75</v>
@@ -7326,7 +7329,7 @@
         <v>78</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>47</v>
@@ -7382,13 +7385,13 @@
         <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>85</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>45</v>
@@ -7397,7 +7400,7 @@
         <v>86</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>47</v>
@@ -7468,7 +7471,7 @@
         <v>96</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>47</v>
@@ -7539,7 +7542,7 @@
         <v>106</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>31</v>
@@ -7610,7 +7613,7 @@
         <v>114</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>31</v>
@@ -7663,16 +7666,16 @@
         <v>119</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>45</v>
@@ -7681,7 +7684,7 @@
         <v>121</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>31</v>
@@ -7734,16 +7737,16 @@
         <v>126</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>29</v>
@@ -7752,7 +7755,7 @@
         <v>128</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>31</v>
@@ -7823,7 +7826,7 @@
         <v>137</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>47</v>
@@ -7956,7 +7959,7 @@
         <v>154</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>29</v>
@@ -7965,7 +7968,7 @@
         <v>155</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>47</v>
@@ -8024,7 +8027,7 @@
         <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>112</v>
@@ -8033,10 +8036,10 @@
         <v>163</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>31</v>
@@ -8092,13 +8095,13 @@
         <v>170</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>171</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>45</v>
@@ -8107,7 +8110,7 @@
         <v>172</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>47</v>
@@ -8163,13 +8166,13 @@
         <v>179</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="I18" s="11" t="s">
+        <v>1626</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>1627</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>1628</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>58</v>
@@ -8231,10 +8234,10 @@
         <v>186</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>1630</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>1631</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>67</v>
@@ -8246,10 +8249,10 @@
         <v>45</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>31</v>
@@ -8320,7 +8323,7 @@
         <v>195</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>31</v>
@@ -8376,7 +8379,7 @@
         <v>201</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>202</v>
@@ -8453,7 +8456,7 @@
         <v>212</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>45</v>
@@ -8462,7 +8465,7 @@
         <v>213</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>31</v>
@@ -8515,7 +8518,7 @@
         <v>218</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>219</v>
@@ -8524,7 +8527,7 @@
         <v>220</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>29</v>
@@ -8533,7 +8536,7 @@
         <v>221</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>47</v>
@@ -8586,7 +8589,7 @@
         <v>226</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>228</v>
@@ -8601,10 +8604,10 @@
         <v>45</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>47</v>
@@ -8660,13 +8663,13 @@
         <v>236</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>237</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>58</v>
@@ -8675,7 +8678,7 @@
         <v>238</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>47</v>
@@ -8731,7 +8734,7 @@
         <v>244</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>245</v>
@@ -8743,10 +8746,10 @@
         <v>45</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>31</v>
@@ -8802,13 +8805,13 @@
         <v>249</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>250</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>45</v>
@@ -8876,7 +8879,7 @@
         <v>257</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>258</v>
@@ -8888,7 +8891,7 @@
         <v>259</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>31</v>
@@ -8950,7 +8953,7 @@
         <v>267</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>45</v>
@@ -8959,7 +8962,7 @@
         <v>268</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>31</v>
@@ -9030,7 +9033,7 @@
         <v>277</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>47</v>
@@ -9089,7 +9092,7 @@
         <v>283</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>285</v>
@@ -9101,7 +9104,7 @@
         <v>286</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>47</v>
@@ -9157,7 +9160,7 @@
         <v>92</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>93</v>
@@ -9172,7 +9175,7 @@
         <v>293</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>294</v>
@@ -9231,7 +9234,7 @@
         <v>300</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>302</v>
@@ -9296,25 +9299,25 @@
         <v>309</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>310</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>47</v>
@@ -9385,7 +9388,7 @@
         <v>320</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>47</v>
@@ -9456,7 +9459,7 @@
         <v>330</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>294</v>
@@ -9509,13 +9512,13 @@
         <v>335</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>336</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>337</v>
@@ -9527,7 +9530,7 @@
         <v>338</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>47</v>
@@ -9583,10 +9586,10 @@
         <v>344</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>345</v>
@@ -9598,7 +9601,7 @@
         <v>346</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>47</v>
@@ -9660,16 +9663,16 @@
         <v>354</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>31</v>
@@ -9678,10 +9681,10 @@
         <v>355</v>
       </c>
       <c r="P39" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="Q39" s="2" t="s">
         <v>1966</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>1967</v>
       </c>
       <c r="R39" s="3" t="s">
         <v>35</v>
@@ -9722,7 +9725,7 @@
         <v>358</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>359</v>
@@ -9731,7 +9734,7 @@
         <v>360</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>29</v>
@@ -9740,7 +9743,7 @@
         <v>361</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>31</v>
@@ -9793,13 +9796,13 @@
         <v>367</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>1667</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>1668</v>
-      </c>
       <c r="I41" s="2" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>368</v>
@@ -9811,7 +9814,7 @@
         <v>369</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>294</v>
@@ -9820,10 +9823,10 @@
         <v>370</v>
       </c>
       <c r="P41" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="Q41" s="2" t="s">
         <v>1968</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>1969</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>35</v>
@@ -9879,10 +9882,10 @@
         <v>45</v>
       </c>
       <c r="L42" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="M42" s="2" t="s">
         <v>1670</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>1671</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>47</v>
@@ -9935,7 +9938,7 @@
         <v>380</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>382</v>
@@ -9944,7 +9947,7 @@
         <v>383</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>45</v>
@@ -9953,7 +9956,7 @@
         <v>384</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>31</v>
@@ -10012,7 +10015,7 @@
         <v>391</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>392</v>
@@ -10021,10 +10024,10 @@
         <v>163</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>47</v>
@@ -10080,13 +10083,13 @@
         <v>399</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="I45" s="11" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>1677</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>1678</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>58</v>
@@ -10095,7 +10098,7 @@
         <v>400</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>47</v>
@@ -10154,7 +10157,7 @@
         <v>407</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>408</v>
@@ -10166,7 +10169,7 @@
         <v>409</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>294</v>
@@ -10237,7 +10240,7 @@
         <v>418</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>47</v>
@@ -10290,7 +10293,7 @@
         <v>423</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>424</v>
@@ -10299,7 +10302,7 @@
         <v>425</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>45</v>
@@ -10308,7 +10311,7 @@
         <v>426</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>47</v>
@@ -10367,10 +10370,10 @@
         <v>433</v>
       </c>
       <c r="I49" s="13" t="s">
+        <v>1684</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>1685</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>1686</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>29</v>
@@ -10379,7 +10382,7 @@
         <v>434</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>294</v>
@@ -10429,28 +10432,28 @@
         <v>350</v>
       </c>
       <c r="F50" s="14" t="s">
+        <v>1983</v>
+      </c>
+      <c r="G50" s="14" t="s">
         <v>1984</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="H50" s="14" t="s">
         <v>1985</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>1986</v>
       </c>
       <c r="I50" s="14" t="s">
         <v>439</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>58</v>
       </c>
       <c r="L50" s="14" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M50" s="14" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="N50" s="15" t="s">
         <v>294</v>
@@ -10509,7 +10512,7 @@
         <v>352</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>446</v>
@@ -10580,19 +10583,19 @@
         <v>352</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L52" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="M52" s="2" t="s">
         <v>1944</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>1945</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>31</v>
@@ -10601,10 +10604,10 @@
         <v>455</v>
       </c>
       <c r="P52" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="Q52" s="2" t="s">
         <v>1946</v>
-      </c>
-      <c r="Q52" s="2" t="s">
-        <v>1947</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>35</v>
@@ -10663,7 +10666,7 @@
         <v>462</v>
       </c>
       <c r="M53" s="14" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="N53" s="15" t="s">
         <v>31</v>
@@ -10731,10 +10734,10 @@
         <v>29</v>
       </c>
       <c r="L54" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="M54" s="2" t="s">
         <v>1948</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>1949</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>47</v>
@@ -10743,10 +10746,10 @@
         <v>472</v>
       </c>
       <c r="P54" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="Q54" s="2" t="s">
         <v>1950</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>1951</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>35</v>
@@ -10855,7 +10858,7 @@
         <v>350</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>481</v>
@@ -10873,10 +10876,10 @@
         <v>45</v>
       </c>
       <c r="L56" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="M56" s="2" t="s">
         <v>1991</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>1992</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>294</v>
@@ -10929,25 +10932,25 @@
         <v>485</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L57" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>1971</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>1972</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>47</v>
@@ -10956,10 +10959,10 @@
         <v>486</v>
       </c>
       <c r="P57" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="Q57" s="2" t="s">
         <v>1973</v>
-      </c>
-      <c r="Q57" s="2" t="s">
-        <v>1974</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>35</v>
@@ -11000,13 +11003,13 @@
         <v>488</v>
       </c>
       <c r="G58" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>1692</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="I58" s="2" t="s">
         <v>1693</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>1694</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>490</v>
@@ -11018,7 +11021,7 @@
         <v>491</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>294</v>
@@ -11074,13 +11077,13 @@
         <v>498</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>497</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>58</v>
@@ -11089,7 +11092,7 @@
         <v>499</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>47</v>
@@ -11160,7 +11163,7 @@
         <v>508</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>294</v>
@@ -11231,7 +11234,7 @@
         <v>518</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>47</v>
@@ -11284,13 +11287,13 @@
         <v>523</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>524</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>525</v>
@@ -11299,10 +11302,10 @@
         <v>58</v>
       </c>
       <c r="L62" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="M62" s="2" t="s">
         <v>1976</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>1977</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>294</v>
@@ -11311,7 +11314,7 @@
         <v>526</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>527</v>
@@ -11358,13 +11361,13 @@
         <v>530</v>
       </c>
       <c r="H63" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>1994</v>
+      </c>
+      <c r="J63" s="2" t="s">
         <v>1702</v>
-      </c>
-      <c r="I63" s="11" t="s">
-        <v>1995</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>1703</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>58</v>
@@ -11373,7 +11376,7 @@
         <v>531</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>47</v>
@@ -11426,10 +11429,10 @@
         <v>536</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>353</v>
@@ -11444,7 +11447,7 @@
         <v>537</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>47</v>
@@ -11497,7 +11500,7 @@
         <v>542</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>445</v>
@@ -11515,7 +11518,7 @@
         <v>545</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>47</v>
@@ -11568,7 +11571,7 @@
         <v>549</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>550</v>
@@ -11577,7 +11580,7 @@
         <v>417</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>29</v>
@@ -11586,7 +11589,7 @@
         <v>551</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>294</v>
@@ -11639,7 +11642,7 @@
         <v>556</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>416</v>
@@ -11657,7 +11660,7 @@
         <v>557</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>47</v>
@@ -11719,16 +11722,16 @@
         <v>564</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L68" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="M68" s="2" t="s">
         <v>1952</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>1953</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>31</v>
@@ -11737,10 +11740,10 @@
         <v>355</v>
       </c>
       <c r="P68" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="Q68" s="2" t="s">
         <v>1954</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>1955</v>
       </c>
       <c r="R68" s="3" t="s">
         <v>35</v>
@@ -11784,13 +11787,13 @@
         <v>570</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>569</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>58</v>
@@ -11799,7 +11802,7 @@
         <v>571</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>47</v>
@@ -11870,7 +11873,7 @@
         <v>580</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>47</v>
@@ -11932,7 +11935,7 @@
         <v>445</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>45</v>
@@ -11941,7 +11944,7 @@
         <v>586</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>47</v>
@@ -11994,13 +11997,13 @@
         <v>591</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>592</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>593</v>
@@ -12009,10 +12012,10 @@
         <v>163</v>
       </c>
       <c r="L72" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M72" s="2" t="s">
         <v>1956</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>1957</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>47</v>
@@ -12021,7 +12024,7 @@
         <v>370</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="Q72" s="2" t="s">
         <v>594</v>
@@ -12080,10 +12083,10 @@
         <v>29</v>
       </c>
       <c r="L73" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="M73" s="2" t="s">
         <v>1979</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>1980</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>294</v>
@@ -12136,7 +12139,7 @@
         <v>603</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>604</v>
@@ -12145,16 +12148,16 @@
         <v>605</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L74" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="M74" s="2" t="s">
         <v>1982</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>1983</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>294</v>
@@ -12216,7 +12219,7 @@
         <v>103</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>45</v>
@@ -12225,7 +12228,7 @@
         <v>610</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>31</v>
@@ -12296,7 +12299,7 @@
         <v>621</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>294</v>
@@ -12367,7 +12370,7 @@
         <v>631</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>294</v>
@@ -12426,10 +12429,10 @@
         <v>490</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>29</v>
@@ -12438,7 +12441,7 @@
         <v>636</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>294</v>
@@ -12500,7 +12503,7 @@
         <v>642</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>29</v>
@@ -12509,7 +12512,7 @@
         <v>644</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>294</v>
@@ -12580,7 +12583,7 @@
         <v>654</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>31</v>
@@ -12651,7 +12654,7 @@
         <v>664</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>31</v>
@@ -12707,10 +12710,10 @@
         <v>352</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>354</v>
@@ -12722,7 +12725,7 @@
         <v>670</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>47</v>
@@ -12784,7 +12787,7 @@
         <v>191</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>29</v>
@@ -12793,7 +12796,7 @@
         <v>675</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>294</v>
@@ -12864,7 +12867,7 @@
         <v>687</v>
       </c>
       <c r="M84" s="14" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="N84" s="15" t="s">
         <v>47</v>
@@ -12923,10 +12926,10 @@
         <v>686</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>45</v>
@@ -12935,7 +12938,7 @@
         <v>695</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>47</v>
@@ -13006,7 +13009,7 @@
         <v>705</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>294</v>
@@ -13077,7 +13080,7 @@
         <v>712</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>31</v>
@@ -13148,7 +13151,7 @@
         <v>722</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="N88" s="3" t="s">
         <v>294</v>
@@ -13219,7 +13222,7 @@
         <v>731</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>47</v>
@@ -13281,7 +13284,7 @@
         <v>740</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>29</v>
@@ -13290,7 +13293,7 @@
         <v>741</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="N90" s="3" t="s">
         <v>31</v>
@@ -13417,34 +13420,34 @@
         <v>757</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>686</v>
+        <v>2014</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>694</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>758</v>
+        <v>2015</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="N92" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O92" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="P92" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="P92" s="2" t="s">
+      <c r="Q92" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="Q92" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="R92" s="3" t="s">
         <v>35</v>
@@ -13467,7 +13470,7 @@
     </row>
     <row r="93" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
@@ -13482,40 +13485,40 @@
         <v>681</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>684</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="N93" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O93" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="P93" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="P93" s="2" t="s">
+      <c r="Q93" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="Q93" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="R93" s="3" t="s">
         <v>35</v>
@@ -13538,7 +13541,7 @@
     </row>
     <row r="94" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>24</v>
@@ -13553,7 +13556,7 @@
         <v>736</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>229</v>
@@ -13571,22 +13574,22 @@
         <v>45</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O94" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="P94" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="P94" s="2" t="s">
+      <c r="Q94" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="Q94" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>35</v>
@@ -13609,7 +13612,7 @@
     </row>
     <row r="95" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>24</v>
@@ -13621,43 +13624,43 @@
         <v>680</v>
       </c>
       <c r="E95" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>778</v>
-      </c>
       <c r="G95" s="2" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H95" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="I95" s="2" t="s">
+      <c r="J95" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O95" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="P95" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="P95" s="2" t="s">
+      <c r="Q95" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="Q95" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="R95" s="3" t="s">
         <v>35</v>
@@ -13680,7 +13683,7 @@
     </row>
     <row r="96" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>24</v>
@@ -13692,19 +13695,19 @@
         <v>680</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F96" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="I96" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>1743</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>381</v>
@@ -13713,22 +13716,22 @@
         <v>163</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O96" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="P96" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="P96" s="2" t="s">
+      <c r="Q96" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="Q96" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="R96" s="3" t="s">
         <v>35</v>
@@ -13751,7 +13754,7 @@
     </row>
     <row r="97" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>24</v>
@@ -13766,40 +13769,40 @@
         <v>681</v>
       </c>
       <c r="F97" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="G97" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="H97" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="I97" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="J97" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>1960</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>798</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L97" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="M97" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O97" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="P97" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="P97" s="2" t="s">
+      <c r="Q97" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="Q97" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="R97" s="3" t="s">
         <v>35</v>
@@ -13822,7 +13825,7 @@
     </row>
     <row r="98" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>24</v>
@@ -13837,40 +13840,40 @@
         <v>736</v>
       </c>
       <c r="F98" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="H98" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="H98" s="2" t="s">
+      <c r="I98" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="I98" s="2" t="s">
+      <c r="J98" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O98" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="P98" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="P98" s="2" t="s">
+      <c r="Q98" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="Q98" s="2" t="s">
-        <v>813</v>
       </c>
       <c r="R98" s="3" t="s">
         <v>35</v>
@@ -13893,7 +13896,7 @@
     </row>
     <row r="99" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>24</v>
@@ -13905,43 +13908,43 @@
         <v>680</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F99" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>1746</v>
-      </c>
-      <c r="H99" s="2" t="s">
+      <c r="I99" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>817</v>
-      </c>
       <c r="J99" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O99" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="P99" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="P99" s="2" t="s">
+      <c r="Q99" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="Q99" s="2" t="s">
-        <v>821</v>
       </c>
       <c r="R99" s="3" t="s">
         <v>35</v>
@@ -13964,7 +13967,7 @@
     </row>
     <row r="100" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>24</v>
@@ -13976,19 +13979,19 @@
         <v>680</v>
       </c>
       <c r="E100" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="G100" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>1748</v>
-      </c>
-      <c r="H100" s="2" t="s">
+      <c r="I100" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>826</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>381</v>
@@ -13997,22 +14000,22 @@
         <v>163</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O100" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="P100" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="P100" s="2" t="s">
+      <c r="Q100" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="Q100" s="2" t="s">
-        <v>830</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>35</v>
@@ -14035,7 +14038,7 @@
     </row>
     <row r="101" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>24</v>
@@ -14047,43 +14050,43 @@
         <v>680</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F101" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>1998</v>
-      </c>
-      <c r="H101" s="2" t="s">
+      <c r="I101" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="I101" s="2" t="s">
+      <c r="J101" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O101" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="P101" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="P101" s="2" t="s">
+      <c r="Q101" s="2" t="s">
         <v>838</v>
-      </c>
-      <c r="Q101" s="2" t="s">
-        <v>839</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>35</v>
@@ -14106,7 +14109,7 @@
     </row>
     <row r="102" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>24</v>
@@ -14121,40 +14124,40 @@
         <v>736</v>
       </c>
       <c r="F102" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H102" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>1751</v>
-      </c>
-      <c r="H102" s="2" t="s">
+      <c r="I102" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="I102" s="2" t="s">
+      <c r="J102" s="2" t="s">
         <v>843</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>844</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>35</v>
@@ -14177,7 +14180,7 @@
     </row>
     <row r="103" spans="1:23" ht="105" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>24</v>
@@ -14189,43 +14192,43 @@
         <v>680</v>
       </c>
       <c r="E103" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="G103" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="I103" s="2" t="s">
         <v>849</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>1753</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>1754</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>850</v>
-      </c>
       <c r="J103" s="2" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="N103" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O103" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="P103" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="P103" s="2" t="s">
+      <c r="Q103" s="2" t="s">
         <v>852</v>
-      </c>
-      <c r="Q103" s="2" t="s">
-        <v>853</v>
       </c>
       <c r="R103" s="3" t="s">
         <v>35</v>
@@ -14248,7 +14251,7 @@
     </row>
     <row r="104" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>24</v>
@@ -14260,43 +14263,43 @@
         <v>680</v>
       </c>
       <c r="E104" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="F104" s="2" t="s">
+      <c r="G104" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="I104" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="G104" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="I104" s="11" t="s">
-        <v>857</v>
-      </c>
       <c r="J104" s="2" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="N104" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O104" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="P104" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="P104" s="2" t="s">
+      <c r="Q104" s="2" t="s">
         <v>862</v>
-      </c>
-      <c r="Q104" s="2" t="s">
-        <v>863</v>
       </c>
       <c r="R104" s="3" t="s">
         <v>35</v>
@@ -14319,7 +14322,7 @@
     </row>
     <row r="105" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>24</v>
@@ -14331,43 +14334,43 @@
         <v>680</v>
       </c>
       <c r="E105" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="F105" s="2" t="s">
+      <c r="G105" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="H105" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J105" s="2" t="s">
         <v>867</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>1758</v>
-      </c>
-      <c r="I105" s="11" t="s">
-        <v>1759</v>
-      </c>
-      <c r="J105" s="2" t="s">
-        <v>868</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="N105" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O105" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="P105" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="P105" s="2" t="s">
+      <c r="Q105" s="2" t="s">
         <v>871</v>
-      </c>
-      <c r="Q105" s="2" t="s">
-        <v>872</v>
       </c>
       <c r="R105" s="3" t="s">
         <v>35</v>
@@ -14390,7 +14393,7 @@
     </row>
     <row r="106" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>24</v>
@@ -14402,43 +14405,43 @@
         <v>680</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>398</v>
       </c>
       <c r="H106" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="I106" s="11" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J106" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="I106" s="11" t="s">
-        <v>1761</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>876</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="N106" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O106" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="P106" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="P106" s="2" t="s">
+      <c r="Q106" s="2" t="s">
         <v>879</v>
-      </c>
-      <c r="Q106" s="2" t="s">
-        <v>880</v>
       </c>
       <c r="R106" s="3" t="s">
         <v>35</v>
@@ -14461,7 +14464,7 @@
     </row>
     <row r="107" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>24</v>
@@ -14473,43 +14476,43 @@
         <v>680</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F107" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>882</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>883</v>
       </c>
       <c r="I107" s="11" t="s">
         <v>398</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="N107" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O107" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="P107" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="P107" s="2" t="s">
+      <c r="Q107" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="Q107" s="2" t="s">
-        <v>888</v>
       </c>
       <c r="R107" s="3" t="s">
         <v>35</v>
@@ -14532,7 +14535,7 @@
     </row>
     <row r="108" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>24</v>
@@ -14544,43 +14547,43 @@
         <v>680</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F108" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="H108" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="I108" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="H108" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="I108" s="2" t="s">
+      <c r="J108" s="2" t="s">
         <v>892</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>893</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="N108" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O108" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="P108" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="P108" s="2" t="s">
+      <c r="Q108" s="2" t="s">
         <v>896</v>
-      </c>
-      <c r="Q108" s="2" t="s">
-        <v>897</v>
       </c>
       <c r="R108" s="3" t="s">
         <v>35</v>
@@ -14603,7 +14606,7 @@
     </row>
     <row r="109" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>24</v>
@@ -14615,43 +14618,43 @@
         <v>680</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F109" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>1768</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>900</v>
-      </c>
       <c r="I109" s="11" t="s">
+        <v>1765</v>
+      </c>
+      <c r="J109" s="2" t="s">
         <v>1766</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>1767</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="N109" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O109" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="P109" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="P109" s="2" t="s">
+      <c r="Q109" s="2" t="s">
         <v>903</v>
-      </c>
-      <c r="Q109" s="2" t="s">
-        <v>904</v>
       </c>
       <c r="R109" s="3" t="s">
         <v>35</v>
@@ -14674,7 +14677,7 @@
     </row>
     <row r="110" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>24</v>
@@ -14686,43 +14689,43 @@
         <v>680</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F110" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>1770</v>
-      </c>
-      <c r="H110" s="2" t="s">
+      <c r="I110" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="I110" s="2" t="s">
+      <c r="J110" s="2" t="s">
         <v>908</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>909</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="N110" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O110" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="P110" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="P110" s="2" t="s">
+      <c r="Q110" s="2" t="s">
         <v>912</v>
-      </c>
-      <c r="Q110" s="2" t="s">
-        <v>913</v>
       </c>
       <c r="R110" s="3" t="s">
         <v>35</v>
@@ -14745,7 +14748,7 @@
     </row>
     <row r="111" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>24</v>
@@ -14757,43 +14760,43 @@
         <v>680</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F111" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="I111" s="11" t="s">
+        <v>1771</v>
+      </c>
+      <c r="J111" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>1774</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>1773</v>
-      </c>
-      <c r="I111" s="11" t="s">
-        <v>1772</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>916</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="N111" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O111" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="P111" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="P111" s="2" t="s">
+      <c r="Q111" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="Q111" s="2" t="s">
-        <v>920</v>
       </c>
       <c r="R111" s="3" t="s">
         <v>35</v>
@@ -14816,7 +14819,7 @@
     </row>
     <row r="112" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>24</v>
@@ -14828,43 +14831,43 @@
         <v>680</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F112" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="H112" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="I112" s="11" t="s">
+        <v>1775</v>
+      </c>
+      <c r="J112" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>1777</v>
-      </c>
-      <c r="I112" s="11" t="s">
-        <v>1776</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>924</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O112" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="P112" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="P112" s="2" t="s">
+      <c r="Q112" s="2" t="s">
         <v>927</v>
-      </c>
-      <c r="Q112" s="2" t="s">
-        <v>928</v>
       </c>
       <c r="R112" s="3" t="s">
         <v>35</v>
@@ -14887,7 +14890,7 @@
     </row>
     <row r="113" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>24</v>
@@ -14899,43 +14902,43 @@
         <v>680</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F113" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="H113" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="I113" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="J113" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="N113" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O113" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="P113" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="P113" s="2" t="s">
+      <c r="Q113" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="Q113" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="R113" s="3" t="s">
         <v>35</v>
@@ -14958,7 +14961,7 @@
     </row>
     <row r="114" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>24</v>
@@ -14967,34 +14970,34 @@
         <v>4</v>
       </c>
       <c r="D114" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>941</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>942</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>92</v>
       </c>
       <c r="I114" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="J114" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>944</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="N114" s="3" t="s">
         <v>31</v>
@@ -15003,10 +15006,10 @@
         <v>713</v>
       </c>
       <c r="P114" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="Q114" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="Q114" s="2" t="s">
-        <v>947</v>
       </c>
       <c r="R114" s="3" t="s">
         <v>35</v>
@@ -15021,7 +15024,7 @@
         <v>36</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W114" s="2" t="s">
         <v>38</v>
@@ -15029,7 +15032,7 @@
     </row>
     <row r="115" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>24</v>
@@ -15038,46 +15041,46 @@
         <v>4</v>
       </c>
       <c r="D115" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F115" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="G115" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="H115" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="I115" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="I115" s="2" t="s">
-        <v>953</v>
-      </c>
       <c r="J115" s="2" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="N115" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O115" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="P115" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="P115" s="2" t="s">
+      <c r="Q115" s="2" t="s">
         <v>957</v>
-      </c>
-      <c r="Q115" s="2" t="s">
-        <v>958</v>
       </c>
       <c r="R115" s="3" t="s">
         <v>35</v>
@@ -15092,7 +15095,7 @@
         <v>36</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W115" s="2" t="s">
         <v>38</v>
@@ -15100,7 +15103,7 @@
     </row>
     <row r="116" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>24</v>
@@ -15109,46 +15112,46 @@
         <v>4</v>
       </c>
       <c r="D116" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F116" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="G116" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="H116" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="I116" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="I116" s="2" t="s">
+      <c r="J116" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="N116" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O116" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="P116" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="P116" s="2" t="s">
-        <v>967</v>
-      </c>
       <c r="Q116" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="R116" s="3" t="s">
         <v>35</v>
@@ -15163,7 +15166,7 @@
         <v>36</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W116" s="2" t="s">
         <v>290</v>
@@ -15171,7 +15174,7 @@
     </row>
     <row r="117" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>24</v>
@@ -15180,34 +15183,34 @@
         <v>4</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F117" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="G117" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="G117" s="2" t="s">
+      <c r="H117" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="H117" s="2" t="s">
+      <c r="I117" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="I117" s="2" t="s">
+      <c r="J117" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="J117" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="N117" s="3" t="s">
         <v>31</v>
@@ -15216,10 +15219,10 @@
         <v>611</v>
       </c>
       <c r="P117" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="Q117" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="Q117" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="R117" s="3" t="s">
         <v>35</v>
@@ -15234,7 +15237,7 @@
         <v>36</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W117" s="2" t="s">
         <v>38</v>
@@ -15242,7 +15245,7 @@
     </row>
     <row r="118" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>24</v>
@@ -15251,46 +15254,46 @@
         <v>4</v>
       </c>
       <c r="D118" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F118" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="I118" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="J118" s="11" t="s">
         <v>1786</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>2001</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="J118" s="11" t="s">
-        <v>1787</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="N118" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O118" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="P118" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="P118" s="2" t="s">
+      <c r="Q118" s="2" t="s">
         <v>982</v>
-      </c>
-      <c r="Q118" s="2" t="s">
-        <v>983</v>
       </c>
       <c r="R118" s="3" t="s">
         <v>35</v>
@@ -15305,7 +15308,7 @@
         <v>36</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W118" s="2" t="s">
         <v>38</v>
@@ -15313,7 +15316,7 @@
     </row>
     <row r="119" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>24</v>
@@ -15322,46 +15325,46 @@
         <v>4</v>
       </c>
       <c r="D119" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E119" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F119" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="I119" s="11" t="s">
         <v>1788</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="J119" s="2" t="s">
         <v>986</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="I119" s="11" t="s">
-        <v>1789</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>987</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="N119" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O119" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="P119" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="P119" s="2" t="s">
+      <c r="Q119" s="2" t="s">
         <v>990</v>
-      </c>
-      <c r="Q119" s="2" t="s">
-        <v>991</v>
       </c>
       <c r="R119" s="3" t="s">
         <v>35</v>
@@ -15376,7 +15379,7 @@
         <v>36</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W119" s="2" t="s">
         <v>38</v>
@@ -15384,7 +15387,7 @@
     </row>
     <row r="120" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>24</v>
@@ -15393,46 +15396,46 @@
         <v>4</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F120" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="G120" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I120" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="J120" s="2" t="s">
         <v>995</v>
-      </c>
-      <c r="J120" s="2" t="s">
-        <v>996</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="N120" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O120" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="P120" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="P120" s="2" t="s">
+      <c r="Q120" s="2" t="s">
         <v>999</v>
-      </c>
-      <c r="Q120" s="2" t="s">
-        <v>1000</v>
       </c>
       <c r="R120" s="3" t="s">
         <v>35</v>
@@ -15447,7 +15450,7 @@
         <v>36</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W120" s="2" t="s">
         <v>38</v>
@@ -15455,7 +15458,7 @@
     </row>
     <row r="121" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>24</v>
@@ -15464,46 +15467,46 @@
         <v>4</v>
       </c>
       <c r="D121" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F121" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G121" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="H121" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="I121" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="H121" s="2" t="s">
-        <v>1793</v>
-      </c>
-      <c r="I121" s="2" t="s">
+      <c r="J121" s="2" t="s">
         <v>1004</v>
-      </c>
-      <c r="J121" s="2" t="s">
-        <v>1005</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="N121" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O121" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P121" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="P121" s="2" t="s">
+      <c r="Q121" s="2" t="s">
         <v>1008</v>
-      </c>
-      <c r="Q121" s="2" t="s">
-        <v>1009</v>
       </c>
       <c r="R121" s="3" t="s">
         <v>35</v>
@@ -15518,7 +15521,7 @@
         <v>36</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W121" s="2" t="s">
         <v>38</v>
@@ -15526,7 +15529,7 @@
     </row>
     <row r="122" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>24</v>
@@ -15535,46 +15538,46 @@
         <v>4</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F122" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I122" s="2" t="s">
         <v>1011</v>
       </c>
-      <c r="G122" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>1012</v>
-      </c>
       <c r="J122" s="11" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="N122" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="P122" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="Q122" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="Q122" s="2" t="s">
-        <v>1015</v>
       </c>
       <c r="R122" s="3" t="s">
         <v>35</v>
@@ -15589,7 +15592,7 @@
         <v>36</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W122" s="2" t="s">
         <v>38</v>
@@ -15597,7 +15600,7 @@
     </row>
     <row r="123" spans="1:23" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.3">
       <c r="A123" s="14" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>24</v>
@@ -15606,46 +15609,46 @@
         <v>4</v>
       </c>
       <c r="D123" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="E123" s="14" t="s">
         <v>939</v>
       </c>
-      <c r="E123" s="14" t="s">
-        <v>940</v>
-      </c>
       <c r="F123" s="14" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G123" s="14" t="s">
         <v>1017</v>
-      </c>
-      <c r="G123" s="14" t="s">
-        <v>1018</v>
       </c>
       <c r="H123" s="14" t="s">
         <v>93</v>
       </c>
       <c r="I123" s="14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J123" s="14" t="s">
         <v>1019</v>
-      </c>
-      <c r="J123" s="14" t="s">
-        <v>1020</v>
       </c>
       <c r="K123" s="16" t="s">
         <v>163</v>
       </c>
       <c r="L123" s="14" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M123" s="14" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="N123" s="15" t="s">
         <v>294</v>
       </c>
       <c r="O123" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="P123" s="14" t="s">
         <v>1022</v>
       </c>
-      <c r="P123" s="14" t="s">
+      <c r="Q123" s="14" t="s">
         <v>1023</v>
-      </c>
-      <c r="Q123" s="14" t="s">
-        <v>1024</v>
       </c>
       <c r="R123" s="15" t="s">
         <v>35</v>
@@ -15660,7 +15663,7 @@
         <v>36</v>
       </c>
       <c r="V123" s="14" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W123" s="14" t="s">
         <v>38</v>
@@ -15668,7 +15671,7 @@
     </row>
     <row r="124" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>24</v>
@@ -15677,46 +15680,46 @@
         <v>4</v>
       </c>
       <c r="D124" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F124" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G124" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="H124" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="I124" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="I124" s="2" t="s">
+      <c r="J124" s="2" t="s">
         <v>1029</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>1030</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L124" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="M124" s="2" t="s">
         <v>1031</v>
-      </c>
-      <c r="M124" s="2" t="s">
-        <v>1032</v>
       </c>
       <c r="N124" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O124" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="P124" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="P124" s="2" t="s">
+      <c r="Q124" s="2" t="s">
         <v>1034</v>
-      </c>
-      <c r="Q124" s="2" t="s">
-        <v>1035</v>
       </c>
       <c r="R124" s="3" t="s">
         <v>35</v>
@@ -15731,7 +15734,7 @@
         <v>36</v>
       </c>
       <c r="V124" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W124" s="2" t="s">
         <v>38</v>
@@ -15739,7 +15742,7 @@
     </row>
     <row r="125" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>24</v>
@@ -15748,46 +15751,46 @@
         <v>4</v>
       </c>
       <c r="D125" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F125" s="2" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="G125" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="I125" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="H125" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>1038</v>
-      </c>
       <c r="J125" s="11" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L125" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="M125" s="2" t="s">
         <v>1962</v>
-      </c>
-      <c r="M125" s="2" t="s">
-        <v>1963</v>
       </c>
       <c r="N125" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O125" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="P125" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="Q125" s="2" t="s">
         <v>1039</v>
-      </c>
-      <c r="P125" s="2" t="s">
-        <v>1964</v>
-      </c>
-      <c r="Q125" s="2" t="s">
-        <v>1040</v>
       </c>
       <c r="R125" s="3" t="s">
         <v>35</v>
@@ -15802,7 +15805,7 @@
         <v>36</v>
       </c>
       <c r="V125" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W125" s="2" t="s">
         <v>38</v>
@@ -15810,7 +15813,7 @@
     </row>
     <row r="126" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>24</v>
@@ -15819,34 +15822,34 @@
         <v>4</v>
       </c>
       <c r="D126" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F126" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H126" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="I126" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="I126" s="2" t="s">
-        <v>944</v>
-      </c>
       <c r="J126" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="N126" s="3" t="s">
         <v>47</v>
@@ -15855,10 +15858,10 @@
         <v>713</v>
       </c>
       <c r="P126" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="Q126" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="Q126" s="2" t="s">
-        <v>1045</v>
       </c>
       <c r="R126" s="3" t="s">
         <v>35</v>
@@ -15873,7 +15876,7 @@
         <v>36</v>
       </c>
       <c r="V126" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W126" s="2" t="s">
         <v>38</v>
@@ -15881,7 +15884,7 @@
     </row>
     <row r="127" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>24</v>
@@ -15890,16 +15893,16 @@
         <v>4</v>
       </c>
       <c r="D127" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E127" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F127" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>94</v>
@@ -15908,28 +15911,28 @@
         <v>93</v>
       </c>
       <c r="J127" s="11" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="N127" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O127" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="P127" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="P127" s="2" t="s">
+      <c r="Q127" s="2" t="s">
         <v>1052</v>
-      </c>
-      <c r="Q127" s="2" t="s">
-        <v>1053</v>
       </c>
       <c r="R127" s="3" t="s">
         <v>35</v>
@@ -15944,7 +15947,7 @@
         <v>36</v>
       </c>
       <c r="V127" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W127" s="2" t="s">
         <v>38</v>
@@ -15952,7 +15955,7 @@
     </row>
     <row r="128" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>24</v>
@@ -15961,46 +15964,46 @@
         <v>4</v>
       </c>
       <c r="D128" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E128" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F128" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G128" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="G128" s="2" t="s">
+      <c r="H128" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="I128" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="I128" s="2" t="s">
+      <c r="J128" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="N128" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O128" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="P128" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="P128" s="2" t="s">
+      <c r="Q128" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="Q128" s="2" t="s">
-        <v>1063</v>
       </c>
       <c r="R128" s="3" t="s">
         <v>35</v>
@@ -16015,7 +16018,7 @@
         <v>36</v>
       </c>
       <c r="V128" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W128" s="2" t="s">
         <v>38</v>
@@ -16023,7 +16026,7 @@
     </row>
     <row r="129" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>24</v>
@@ -16032,46 +16035,46 @@
         <v>4</v>
       </c>
       <c r="D129" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E129" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F129" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G129" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="H129" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J129" s="11" t="s">
         <v>1066</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>1067</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="N129" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O129" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="P129" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="P129" s="2" t="s">
+      <c r="Q129" s="2" t="s">
         <v>1072</v>
-      </c>
-      <c r="Q129" s="2" t="s">
-        <v>1073</v>
       </c>
       <c r="R129" s="3" t="s">
         <v>35</v>
@@ -16086,7 +16089,7 @@
         <v>36</v>
       </c>
       <c r="V129" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W129" s="2" t="s">
         <v>38</v>
@@ -16094,7 +16097,7 @@
     </row>
     <row r="130" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>24</v>
@@ -16103,46 +16106,46 @@
         <v>4</v>
       </c>
       <c r="D130" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E130" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F130" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="N130" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="P130" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Q130" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="Q130" s="2" t="s">
-        <v>1078</v>
       </c>
       <c r="R130" s="3" t="s">
         <v>35</v>
@@ -16157,7 +16160,7 @@
         <v>36</v>
       </c>
       <c r="V130" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W130" s="2" t="s">
         <v>38</v>
@@ -16165,7 +16168,7 @@
     </row>
     <row r="131" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>24</v>
@@ -16174,46 +16177,46 @@
         <v>4</v>
       </c>
       <c r="D131" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F131" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="N131" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O131" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="P131" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="P131" s="2" t="s">
+      <c r="Q131" s="2" t="s">
         <v>1083</v>
-      </c>
-      <c r="Q131" s="2" t="s">
-        <v>1084</v>
       </c>
       <c r="R131" s="3" t="s">
         <v>35</v>
@@ -16228,7 +16231,7 @@
         <v>36</v>
       </c>
       <c r="V131" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W131" s="2" t="s">
         <v>38</v>
@@ -16236,7 +16239,7 @@
     </row>
     <row r="132" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>24</v>
@@ -16245,46 +16248,46 @@
         <v>4</v>
       </c>
       <c r="D132" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F132" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="G132" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="H132" s="2" t="s">
+      <c r="I132" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="I132" s="2" t="s">
-        <v>1088</v>
-      </c>
       <c r="J132" s="11" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="N132" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O132" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P132" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="P132" s="2" t="s">
-        <v>1092</v>
-      </c>
       <c r="Q132" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R132" s="3" t="s">
         <v>35</v>
@@ -16299,7 +16302,7 @@
         <v>36</v>
       </c>
       <c r="V132" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W132" s="2" t="s">
         <v>38</v>
@@ -16307,7 +16310,7 @@
     </row>
     <row r="133" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>24</v>
@@ -16316,46 +16319,46 @@
         <v>4</v>
       </c>
       <c r="D133" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>940</v>
-      </c>
       <c r="F133" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="H133" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="H133" s="2" t="s">
-        <v>1096</v>
-      </c>
       <c r="I133" s="2" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="N133" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O133" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="P133" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="P133" s="2" t="s">
+      <c r="Q133" s="2" t="s">
         <v>1099</v>
-      </c>
-      <c r="Q133" s="2" t="s">
-        <v>1100</v>
       </c>
       <c r="R133" s="3" t="s">
         <v>35</v>
@@ -16370,7 +16373,7 @@
         <v>36</v>
       </c>
       <c r="V133" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W133" s="2" t="s">
         <v>38</v>
@@ -16378,7 +16381,7 @@
     </row>
     <row r="134" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>24</v>
@@ -16387,46 +16390,46 @@
         <v>4</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E134" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="G134" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="H134" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="H134" s="2" t="s">
+      <c r="I134" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="J134" s="11" t="s">
         <v>1105</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="J134" s="11" t="s">
-        <v>1106</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="N134" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O134" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="P134" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="P134" s="2" t="s">
+      <c r="Q134" s="2" t="s">
         <v>1110</v>
-      </c>
-      <c r="Q134" s="2" t="s">
-        <v>1111</v>
       </c>
       <c r="R134" s="3" t="s">
         <v>35</v>
@@ -16441,7 +16444,7 @@
         <v>36</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W134" s="2" t="s">
         <v>38</v>
@@ -16449,7 +16452,7 @@
     </row>
     <row r="135" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>24</v>
@@ -16458,46 +16461,46 @@
         <v>4</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F135" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G135" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="G135" s="2" t="s">
+      <c r="H135" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="H135" s="2" t="s">
+      <c r="I135" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="I135" s="2" t="s">
+      <c r="J135" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>1117</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L135" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="N135" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O135" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="P135" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="P135" s="2" t="s">
+      <c r="Q135" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="Q135" s="2" t="s">
-        <v>1121</v>
       </c>
       <c r="R135" s="3" t="s">
         <v>35</v>
@@ -16512,7 +16515,7 @@
         <v>36</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W135" s="2" t="s">
         <v>290</v>
@@ -16520,7 +16523,7 @@
     </row>
     <row r="136" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>24</v>
@@ -16529,46 +16532,46 @@
         <v>4</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F136" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G136" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="H136" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I136" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="H136" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I136" s="2" t="s">
-        <v>1125</v>
-      </c>
       <c r="J136" s="2" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L136" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="N136" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O136" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="P136" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="P136" s="2" t="s">
+      <c r="Q136" s="2" t="s">
         <v>1129</v>
-      </c>
-      <c r="Q136" s="2" t="s">
-        <v>1130</v>
       </c>
       <c r="R136" s="3" t="s">
         <v>35</v>
@@ -16583,7 +16586,7 @@
         <v>36</v>
       </c>
       <c r="V136" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W136" s="2" t="s">
         <v>38</v>
@@ -16591,7 +16594,7 @@
     </row>
     <row r="137" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>24</v>
@@ -16600,46 +16603,46 @@
         <v>4</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G137" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="H137" s="2" t="s">
         <v>1813</v>
       </c>
-      <c r="H137" s="2" t="s">
+      <c r="I137" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="I137" s="2" t="s">
+      <c r="J137" s="2" t="s">
         <v>1815</v>
-      </c>
-      <c r="J137" s="2" t="s">
-        <v>1816</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="N137" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O137" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="P137" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="P137" s="2" t="s">
+      <c r="Q137" s="2" t="s">
         <v>1135</v>
-      </c>
-      <c r="Q137" s="2" t="s">
-        <v>1136</v>
       </c>
       <c r="R137" s="3" t="s">
         <v>35</v>
@@ -16654,7 +16657,7 @@
         <v>36</v>
       </c>
       <c r="V137" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W137" s="2" t="s">
         <v>38</v>
@@ -16662,7 +16665,7 @@
     </row>
     <row r="138" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>24</v>
@@ -16671,46 +16674,46 @@
         <v>4</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F138" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H138" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="G138" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H138" s="2" t="s">
+      <c r="I138" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="I138" s="2" t="s">
-        <v>1140</v>
-      </c>
       <c r="J138" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="N138" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O138" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="P138" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="P138" s="2" t="s">
+      <c r="Q138" s="2" t="s">
         <v>1135</v>
-      </c>
-      <c r="Q138" s="2" t="s">
-        <v>1136</v>
       </c>
       <c r="R138" s="3" t="s">
         <v>35</v>
@@ -16725,7 +16728,7 @@
         <v>36</v>
       </c>
       <c r="V138" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W138" s="2" t="s">
         <v>38</v>
@@ -16733,7 +16736,7 @@
     </row>
     <row r="139" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>24</v>
@@ -16742,46 +16745,46 @@
         <v>4</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F139" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="G139" s="2" t="s">
+      <c r="H139" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="H139" s="2" t="s">
+      <c r="I139" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="I139" s="2" t="s">
-        <v>1147</v>
-      </c>
       <c r="J139" s="11" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L139" s="2" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="N139" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="P139" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="Q139" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="Q139" s="2" t="s">
-        <v>1150</v>
       </c>
       <c r="R139" s="3" t="s">
         <v>35</v>
@@ -16796,7 +16799,7 @@
         <v>36</v>
       </c>
       <c r="V139" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W139" s="2" t="s">
         <v>38</v>
@@ -16804,7 +16807,7 @@
     </row>
     <row r="140" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>24</v>
@@ -16813,46 +16816,46 @@
         <v>4</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F140" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G140" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="H140" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="H140" s="2" t="s">
+      <c r="I140" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="I140" s="2" t="s">
+      <c r="J140" s="2" t="s">
         <v>1155</v>
-      </c>
-      <c r="J140" s="2" t="s">
-        <v>1156</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N140" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O140" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P140" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="P140" s="2" t="s">
+      <c r="Q140" s="2" t="s">
         <v>1159</v>
-      </c>
-      <c r="Q140" s="2" t="s">
-        <v>1160</v>
       </c>
       <c r="R140" s="3" t="s">
         <v>35</v>
@@ -16867,7 +16870,7 @@
         <v>36</v>
       </c>
       <c r="V140" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W140" s="2" t="s">
         <v>290</v>
@@ -16875,7 +16878,7 @@
     </row>
     <row r="141" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>24</v>
@@ -16884,13 +16887,13 @@
         <v>4</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>569</v>
@@ -16899,31 +16902,31 @@
         <v>568</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="J141" s="11" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="N141" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O141" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="P141" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="P141" s="2" t="s">
+      <c r="Q141" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="Q141" s="2" t="s">
-        <v>1167</v>
       </c>
       <c r="R141" s="3" t="s">
         <v>35</v>
@@ -16938,7 +16941,7 @@
         <v>36</v>
       </c>
       <c r="V141" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W141" s="2" t="s">
         <v>38</v>
@@ -16946,7 +16949,7 @@
     </row>
     <row r="142" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>24</v>
@@ -16955,46 +16958,46 @@
         <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F142" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I142" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="G142" s="2" t="s">
+      <c r="J142" s="11" t="s">
         <v>1139</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I142" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="J142" s="11" t="s">
-        <v>1140</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="N142" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O142" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="P142" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="P142" s="2" t="s">
+      <c r="Q142" s="2" t="s">
         <v>1173</v>
-      </c>
-      <c r="Q142" s="2" t="s">
-        <v>1174</v>
       </c>
       <c r="R142" s="3" t="s">
         <v>35</v>
@@ -17009,7 +17012,7 @@
         <v>36</v>
       </c>
       <c r="V142" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W142" s="2" t="s">
         <v>38</v>
@@ -17017,7 +17020,7 @@
     </row>
     <row r="143" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>24</v>
@@ -17026,46 +17029,46 @@
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F143" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G143" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="G143" s="2" t="s">
+      <c r="H143" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="H143" s="2" t="s">
+      <c r="I143" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="J143" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="I143" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="J143" s="2" t="s">
-        <v>1179</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="N143" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="P143" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="Q143" s="2" t="s">
         <v>1181</v>
-      </c>
-      <c r="Q143" s="2" t="s">
-        <v>1182</v>
       </c>
       <c r="R143" s="3" t="s">
         <v>35</v>
@@ -17080,7 +17083,7 @@
         <v>36</v>
       </c>
       <c r="V143" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W143" s="2" t="s">
         <v>38</v>
@@ -17088,7 +17091,7 @@
     </row>
     <row r="144" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>24</v>
@@ -17097,46 +17100,46 @@
         <v>4</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F144" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G144" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="G144" s="2" t="s">
+      <c r="H144" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="H144" s="2" t="s">
+      <c r="I144" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="J144" s="2" t="s">
         <v>1186</v>
-      </c>
-      <c r="I144" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>1187</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L144" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="N144" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O144" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="P144" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="P144" s="2" t="s">
+      <c r="Q144" s="2" t="s">
         <v>1190</v>
-      </c>
-      <c r="Q144" s="2" t="s">
-        <v>1191</v>
       </c>
       <c r="R144" s="3" t="s">
         <v>35</v>
@@ -17151,7 +17154,7 @@
         <v>36</v>
       </c>
       <c r="V144" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W144" s="2" t="s">
         <v>290</v>
@@ -17159,7 +17162,7 @@
     </row>
     <row r="145" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>24</v>
@@ -17168,46 +17171,46 @@
         <v>4</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F145" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G145" s="2" t="s">
         <v>1193</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="H145" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I145" s="11" t="s">
         <v>1194</v>
       </c>
-      <c r="H145" s="2" t="s">
+      <c r="J145" s="2" t="s">
         <v>1196</v>
-      </c>
-      <c r="I145" s="11" t="s">
-        <v>1195</v>
-      </c>
-      <c r="J145" s="2" t="s">
-        <v>1197</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="N145" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O145" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="P145" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="P145" s="2" t="s">
+      <c r="Q145" s="2" t="s">
         <v>1200</v>
-      </c>
-      <c r="Q145" s="2" t="s">
-        <v>1201</v>
       </c>
       <c r="R145" s="3" t="s">
         <v>35</v>
@@ -17222,7 +17225,7 @@
         <v>36</v>
       </c>
       <c r="V145" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W145" s="2" t="s">
         <v>290</v>
@@ -17230,7 +17233,7 @@
     </row>
     <row r="146" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>24</v>
@@ -17239,46 +17242,46 @@
         <v>4</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F146" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H146" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="G146" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>1204</v>
-      </c>
       <c r="I146" s="11" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="J146" s="11" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L146" s="2" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="N146" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O146" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="P146" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="P146" s="2" t="s">
+      <c r="Q146" s="2" t="s">
         <v>1207</v>
-      </c>
-      <c r="Q146" s="2" t="s">
-        <v>1208</v>
       </c>
       <c r="R146" s="3" t="s">
         <v>35</v>
@@ -17293,7 +17296,7 @@
         <v>36</v>
       </c>
       <c r="V146" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W146" s="2" t="s">
         <v>38</v>
@@ -17301,7 +17304,7 @@
     </row>
     <row r="147" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>24</v>
@@ -17310,46 +17313,46 @@
         <v>4</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E147" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="F147" s="2" t="s">
-        <v>1211</v>
-      </c>
       <c r="G147" s="2" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="J147" s="11" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L147" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="N147" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O147" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="P147" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="P147" s="2" t="s">
+      <c r="Q147" s="2" t="s">
         <v>1216</v>
-      </c>
-      <c r="Q147" s="2" t="s">
-        <v>1217</v>
       </c>
       <c r="R147" s="3" t="s">
         <v>35</v>
@@ -17364,7 +17367,7 @@
         <v>36</v>
       </c>
       <c r="V147" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W147" s="2" t="s">
         <v>38</v>
@@ -17372,7 +17375,7 @@
     </row>
     <row r="148" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>24</v>
@@ -17381,46 +17384,46 @@
         <v>4</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F148" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H148" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="I148" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J148" s="11" t="s">
         <v>1835</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>1220</v>
-      </c>
-      <c r="I148" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="J148" s="11" t="s">
-        <v>1836</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L148" s="2" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="N148" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O148" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="P148" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="P148" s="2" t="s">
+      <c r="Q148" s="2" t="s">
         <v>1223</v>
-      </c>
-      <c r="Q148" s="2" t="s">
-        <v>1224</v>
       </c>
       <c r="R148" s="3" t="s">
         <v>35</v>
@@ -17435,7 +17438,7 @@
         <v>36</v>
       </c>
       <c r="V148" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W148" s="2" t="s">
         <v>38</v>
@@ -17443,7 +17446,7 @@
     </row>
     <row r="149" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>24</v>
@@ -17452,46 +17455,46 @@
         <v>4</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F149" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G149" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="G149" s="2" t="s">
-        <v>1227</v>
-      </c>
       <c r="H149" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J149" s="11" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="N149" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="P149" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="Q149" s="2" t="s">
         <v>1230</v>
-      </c>
-      <c r="Q149" s="2" t="s">
-        <v>1231</v>
       </c>
       <c r="R149" s="3" t="s">
         <v>35</v>
@@ -17506,7 +17509,7 @@
         <v>36</v>
       </c>
       <c r="V149" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W149" s="2" t="s">
         <v>38</v>
@@ -17514,7 +17517,7 @@
     </row>
     <row r="150" spans="1:23" ht="120" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>24</v>
@@ -17523,46 +17526,46 @@
         <v>4</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="J150" s="11" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="N150" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O150" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="P150" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="P150" s="2" t="s">
+      <c r="Q150" s="2" t="s">
         <v>1235</v>
-      </c>
-      <c r="Q150" s="2" t="s">
-        <v>1236</v>
       </c>
       <c r="R150" s="3" t="s">
         <v>35</v>
@@ -17577,7 +17580,7 @@
         <v>36</v>
       </c>
       <c r="V150" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W150" s="2" t="s">
         <v>38</v>
@@ -17585,7 +17588,7 @@
     </row>
     <row r="151" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>24</v>
@@ -17594,46 +17597,46 @@
         <v>4</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="N151" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="P151" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="Q151" s="2" t="s">
         <v>1239</v>
-      </c>
-      <c r="Q151" s="2" t="s">
-        <v>1240</v>
       </c>
       <c r="R151" s="3" t="s">
         <v>35</v>
@@ -17648,7 +17651,7 @@
         <v>36</v>
       </c>
       <c r="V151" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W151" s="2" t="s">
         <v>38</v>
@@ -17656,7 +17659,7 @@
     </row>
     <row r="152" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>24</v>
@@ -17665,46 +17668,46 @@
         <v>4</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F152" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I152" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="G152" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="H152" s="2" t="s">
+      <c r="J152" s="2" t="s">
         <v>1212</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="J152" s="2" t="s">
-        <v>1213</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="N152" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O152" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="P152" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="P152" s="2" t="s">
+      <c r="Q152" s="2" t="s">
         <v>1245</v>
-      </c>
-      <c r="Q152" s="2" t="s">
-        <v>1246</v>
       </c>
       <c r="R152" s="3" t="s">
         <v>35</v>
@@ -17719,7 +17722,7 @@
         <v>36</v>
       </c>
       <c r="V152" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W152" s="2" t="s">
         <v>38</v>
@@ -17727,7 +17730,7 @@
     </row>
     <row r="153" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>24</v>
@@ -17736,46 +17739,46 @@
         <v>4</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F153" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I153" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="G153" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>1249</v>
-      </c>
       <c r="J153" s="11" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="N153" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O153" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="P153" s="2" t="s">
         <v>1250</v>
       </c>
-      <c r="P153" s="2" t="s">
+      <c r="Q153" s="2" t="s">
         <v>1251</v>
-      </c>
-      <c r="Q153" s="2" t="s">
-        <v>1252</v>
       </c>
       <c r="R153" s="3" t="s">
         <v>35</v>
@@ -17790,7 +17793,7 @@
         <v>36</v>
       </c>
       <c r="V153" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W153" s="2" t="s">
         <v>38</v>
@@ -17798,7 +17801,7 @@
     </row>
     <row r="154" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>24</v>
@@ -17807,46 +17810,46 @@
         <v>4</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F154" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G154" s="2" t="s">
         <v>1254</v>
       </c>
-      <c r="G154" s="2" t="s">
-        <v>1255</v>
-      </c>
       <c r="H154" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="N154" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O154" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P154" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="P154" s="2" t="s">
+      <c r="Q154" s="2" t="s">
         <v>1258</v>
-      </c>
-      <c r="Q154" s="2" t="s">
-        <v>1259</v>
       </c>
       <c r="R154" s="3" t="s">
         <v>35</v>
@@ -17861,7 +17864,7 @@
         <v>36</v>
       </c>
       <c r="V154" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W154" s="2" t="s">
         <v>38</v>
@@ -17869,7 +17872,7 @@
     </row>
     <row r="155" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>24</v>
@@ -17878,46 +17881,46 @@
         <v>4</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F155" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G155" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="H155" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="H155" s="2" t="s">
+      <c r="I155" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="I155" s="2" t="s">
+      <c r="J155" s="2" t="s">
         <v>1264</v>
-      </c>
-      <c r="J155" s="2" t="s">
-        <v>1265</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="N155" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O155" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="P155" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="P155" s="2" t="s">
+      <c r="Q155" s="2" t="s">
         <v>1268</v>
-      </c>
-      <c r="Q155" s="2" t="s">
-        <v>1269</v>
       </c>
       <c r="R155" s="3" t="s">
         <v>35</v>
@@ -17932,7 +17935,7 @@
         <v>36</v>
       </c>
       <c r="V155" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W155" s="2" t="s">
         <v>290</v>
@@ -17940,7 +17943,7 @@
     </row>
     <row r="156" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>24</v>
@@ -17949,46 +17952,46 @@
         <v>4</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F156" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G156" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="H156" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="H156" s="2" t="s">
+      <c r="I156" s="2" t="s">
         <v>1273</v>
       </c>
-      <c r="I156" s="2" t="s">
-        <v>1274</v>
-      </c>
       <c r="J156" s="2" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="N156" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O156" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="P156" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="P156" s="2" t="s">
+      <c r="Q156" s="2" t="s">
         <v>1277</v>
-      </c>
-      <c r="Q156" s="2" t="s">
-        <v>1278</v>
       </c>
       <c r="R156" s="3" t="s">
         <v>35</v>
@@ -18003,7 +18006,7 @@
         <v>36</v>
       </c>
       <c r="V156" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W156" s="2" t="s">
         <v>38</v>
@@ -18011,7 +18014,7 @@
     </row>
     <row r="157" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>24</v>
@@ -18020,46 +18023,46 @@
         <v>4</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G157" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H157" s="2" t="s">
         <v>1212</v>
       </c>
-      <c r="H157" s="2" t="s">
-        <v>1213</v>
-      </c>
       <c r="I157" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="J157" s="2" t="s">
         <v>1856</v>
-      </c>
-      <c r="J157" s="2" t="s">
-        <v>1857</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L157" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="M157" s="2" t="s">
         <v>1858</v>
-      </c>
-      <c r="M157" s="2" t="s">
-        <v>1859</v>
       </c>
       <c r="N157" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="P157" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Q157" s="2" t="s">
         <v>1281</v>
-      </c>
-      <c r="Q157" s="2" t="s">
-        <v>1282</v>
       </c>
       <c r="R157" s="3" t="s">
         <v>35</v>
@@ -18074,7 +18077,7 @@
         <v>36</v>
       </c>
       <c r="V157" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W157" s="2" t="s">
         <v>38</v>
@@ -18082,7 +18085,7 @@
     </row>
     <row r="158" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>24</v>
@@ -18091,46 +18094,46 @@
         <v>4</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F158" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="H158" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="G158" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="H158" s="2" t="s">
+      <c r="I158" s="11" t="s">
+        <v>1859</v>
+      </c>
+      <c r="J158" s="2" t="s">
         <v>1285</v>
-      </c>
-      <c r="I158" s="11" t="s">
-        <v>1860</v>
-      </c>
-      <c r="J158" s="2" t="s">
-        <v>1286</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="N158" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O158" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="P158" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="P158" s="2" t="s">
+      <c r="Q158" s="2" t="s">
         <v>1289</v>
-      </c>
-      <c r="Q158" s="2" t="s">
-        <v>1290</v>
       </c>
       <c r="R158" s="3" t="s">
         <v>35</v>
@@ -18145,7 +18148,7 @@
         <v>36</v>
       </c>
       <c r="V158" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W158" s="2" t="s">
         <v>290</v>
@@ -18153,7 +18156,7 @@
     </row>
     <row r="159" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>24</v>
@@ -18162,46 +18165,46 @@
         <v>4</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F159" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I159" s="2" t="s">
         <v>1292</v>
       </c>
-      <c r="G159" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H159" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="I159" s="2" t="s">
-        <v>1293</v>
-      </c>
       <c r="J159" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L159" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="N159" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O159" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="P159" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="P159" s="2" t="s">
+      <c r="Q159" s="2" t="s">
         <v>1296</v>
-      </c>
-      <c r="Q159" s="2" t="s">
-        <v>1297</v>
       </c>
       <c r="R159" s="3" t="s">
         <v>35</v>
@@ -18216,7 +18219,7 @@
         <v>36</v>
       </c>
       <c r="V159" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W159" s="2" t="s">
         <v>38</v>
@@ -18224,7 +18227,7 @@
     </row>
     <row r="160" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>24</v>
@@ -18233,16 +18236,16 @@
         <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F160" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G160" s="2" t="s">
         <v>1299</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>1300</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>194</v>
@@ -18251,28 +18254,28 @@
         <v>191</v>
       </c>
       <c r="J160" s="11" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="N160" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O160" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="P160" s="2" t="s">
         <v>1302</v>
       </c>
-      <c r="P160" s="2" t="s">
+      <c r="Q160" s="2" t="s">
         <v>1303</v>
-      </c>
-      <c r="Q160" s="2" t="s">
-        <v>1304</v>
       </c>
       <c r="R160" s="3" t="s">
         <v>35</v>
@@ -18287,7 +18290,7 @@
         <v>36</v>
       </c>
       <c r="V160" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W160" s="2" t="s">
         <v>38</v>
@@ -18295,7 +18298,7 @@
     </row>
     <row r="161" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>24</v>
@@ -18304,46 +18307,46 @@
         <v>5</v>
       </c>
       <c r="D161" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E161" s="2" t="s">
+      <c r="F161" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="F161" s="2" t="s">
+      <c r="G161" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>1309</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>569</v>
       </c>
       <c r="I161" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J161" s="2" t="s">
         <v>1310</v>
-      </c>
-      <c r="J161" s="2" t="s">
-        <v>1311</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="N161" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O161" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="P161" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="P161" s="2" t="s">
+      <c r="Q161" s="2" t="s">
         <v>1313</v>
-      </c>
-      <c r="Q161" s="2" t="s">
-        <v>1314</v>
       </c>
       <c r="R161" s="3" t="s">
         <v>35</v>
@@ -18358,7 +18361,7 @@
         <v>36</v>
       </c>
       <c r="V161" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W161" s="2" t="s">
         <v>38</v>
@@ -18366,7 +18369,7 @@
     </row>
     <row r="162" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>24</v>
@@ -18375,46 +18378,46 @@
         <v>5</v>
       </c>
       <c r="D162" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E162" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F162" s="2" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="I162" s="2" t="s">
         <v>569</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="N162" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O162" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="P162" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="Q162" s="2" t="s">
         <v>1320</v>
-      </c>
-      <c r="Q162" s="2" t="s">
-        <v>1321</v>
       </c>
       <c r="R162" s="3" t="s">
         <v>35</v>
@@ -18429,7 +18432,7 @@
         <v>36</v>
       </c>
       <c r="V162" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W162" s="2" t="s">
         <v>38</v>
@@ -18437,7 +18440,7 @@
     </row>
     <row r="163" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>24</v>
@@ -18446,46 +18449,46 @@
         <v>5</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E163" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F163" s="2" t="s">
         <v>1323</v>
       </c>
-      <c r="F163" s="2" t="s">
+      <c r="G163" s="2" t="s">
         <v>1324</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="H163" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="H163" s="2" t="s">
+      <c r="I163" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="I163" s="2" t="s">
+      <c r="J163" s="2" t="s">
         <v>1327</v>
-      </c>
-      <c r="J163" s="2" t="s">
-        <v>1328</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="N163" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O163" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="P163" s="2" t="s">
         <v>1330</v>
       </c>
-      <c r="P163" s="2" t="s">
+      <c r="Q163" s="2" t="s">
         <v>1331</v>
-      </c>
-      <c r="Q163" s="2" t="s">
-        <v>1332</v>
       </c>
       <c r="R163" s="3" t="s">
         <v>35</v>
@@ -18500,7 +18503,7 @@
         <v>36</v>
       </c>
       <c r="V163" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W163" s="2" t="s">
         <v>38</v>
@@ -18508,7 +18511,7 @@
     </row>
     <row r="164" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>24</v>
@@ -18517,46 +18520,46 @@
         <v>5</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F164" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G164" s="2" t="s">
         <v>1334</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="H164" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="H164" s="2" t="s">
+      <c r="I164" s="2" t="s">
         <v>1336</v>
       </c>
-      <c r="I164" s="2" t="s">
+      <c r="J164" s="2" t="s">
         <v>1337</v>
-      </c>
-      <c r="J164" s="2" t="s">
-        <v>1338</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="N164" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O164" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="P164" s="2" t="s">
         <v>1340</v>
       </c>
-      <c r="P164" s="2" t="s">
+      <c r="Q164" s="2" t="s">
         <v>1341</v>
-      </c>
-      <c r="Q164" s="2" t="s">
-        <v>1342</v>
       </c>
       <c r="R164" s="3" t="s">
         <v>35</v>
@@ -18571,7 +18574,7 @@
         <v>36</v>
       </c>
       <c r="V164" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W164" s="2" t="s">
         <v>290</v>
@@ -18579,7 +18582,7 @@
     </row>
     <row r="165" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>24</v>
@@ -18588,46 +18591,46 @@
         <v>5</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F165" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H165" s="2" t="s">
         <v>1344</v>
       </c>
-      <c r="G165" s="2" t="s">
-        <v>1347</v>
-      </c>
-      <c r="H165" s="2" t="s">
+      <c r="I165" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="I165" s="2" t="s">
-        <v>1346</v>
-      </c>
       <c r="J165" s="11" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="N165" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O165" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="P165" s="2" t="s">
         <v>1349</v>
       </c>
-      <c r="P165" s="2" t="s">
+      <c r="Q165" s="2" t="s">
         <v>1350</v>
-      </c>
-      <c r="Q165" s="2" t="s">
-        <v>1351</v>
       </c>
       <c r="R165" s="3" t="s">
         <v>35</v>
@@ -18642,7 +18645,7 @@
         <v>36</v>
       </c>
       <c r="V165" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W165" s="2" t="s">
         <v>38</v>
@@ -18650,7 +18653,7 @@
     </row>
     <row r="166" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>24</v>
@@ -18659,46 +18662,46 @@
         <v>5</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E166" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>1353</v>
       </c>
-      <c r="F166" s="2" t="s">
+      <c r="G166" s="2" t="s">
         <v>1354</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="H166" s="2" t="s">
         <v>1355</v>
       </c>
-      <c r="H166" s="2" t="s">
+      <c r="I166" s="2" t="s">
         <v>1356</v>
       </c>
-      <c r="I166" s="2" t="s">
+      <c r="J166" s="2" t="s">
         <v>1357</v>
-      </c>
-      <c r="J166" s="2" t="s">
-        <v>1358</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="N166" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O166" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="P166" s="2" t="s">
         <v>1360</v>
       </c>
-      <c r="P166" s="2" t="s">
+      <c r="Q166" s="2" t="s">
         <v>1361</v>
-      </c>
-      <c r="Q166" s="2" t="s">
-        <v>1362</v>
       </c>
       <c r="R166" s="3" t="s">
         <v>35</v>
@@ -18713,7 +18716,7 @@
         <v>36</v>
       </c>
       <c r="V166" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W166" s="2" t="s">
         <v>290</v>
@@ -18721,7 +18724,7 @@
     </row>
     <row r="167" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>24</v>
@@ -18730,46 +18733,46 @@
         <v>5</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F167" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G167" s="2" t="s">
         <v>1364</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="H167" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="I167" s="2" t="s">
         <v>1365</v>
       </c>
-      <c r="H167" s="2" t="s">
-        <v>1872</v>
-      </c>
-      <c r="I167" s="2" t="s">
-        <v>1366</v>
-      </c>
       <c r="J167" s="11" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="N167" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O167" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="P167" s="2" t="s">
         <v>1368</v>
       </c>
-      <c r="P167" s="2" t="s">
+      <c r="Q167" s="2" t="s">
         <v>1369</v>
-      </c>
-      <c r="Q167" s="2" t="s">
-        <v>1370</v>
       </c>
       <c r="R167" s="3" t="s">
         <v>35</v>
@@ -18784,7 +18787,7 @@
         <v>36</v>
       </c>
       <c r="V167" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W167" s="2" t="s">
         <v>38</v>
@@ -18792,7 +18795,7 @@
     </row>
     <row r="168" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>24</v>
@@ -18801,46 +18804,46 @@
         <v>5</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F168" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="I168" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="G168" s="2" t="s">
-        <v>1876</v>
-      </c>
-      <c r="H168" s="2" t="s">
-        <v>1875</v>
-      </c>
-      <c r="I168" s="2" t="s">
-        <v>1373</v>
-      </c>
       <c r="J168" s="2" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="N168" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O168" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="P168" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="P168" s="2" t="s">
+      <c r="Q168" s="2" t="s">
         <v>1376</v>
-      </c>
-      <c r="Q168" s="2" t="s">
-        <v>1377</v>
       </c>
       <c r="R168" s="3" t="s">
         <v>35</v>
@@ -18855,7 +18858,7 @@
         <v>36</v>
       </c>
       <c r="V168" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W168" s="2" t="s">
         <v>38</v>
@@ -18863,7 +18866,7 @@
     </row>
     <row r="169" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>24</v>
@@ -18872,46 +18875,46 @@
         <v>5</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F169" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G169" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="H169" s="2" t="s">
         <v>1380</v>
       </c>
-      <c r="H169" s="2" t="s">
+      <c r="I169" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="I169" s="2" t="s">
+      <c r="J169" s="2" t="s">
         <v>1382</v>
-      </c>
-      <c r="J169" s="2" t="s">
-        <v>1383</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="N169" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O169" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="P169" s="2" t="s">
         <v>1385</v>
       </c>
-      <c r="P169" s="2" t="s">
+      <c r="Q169" s="2" t="s">
         <v>1386</v>
-      </c>
-      <c r="Q169" s="2" t="s">
-        <v>1387</v>
       </c>
       <c r="R169" s="3" t="s">
         <v>35</v>
@@ -18926,7 +18929,7 @@
         <v>36</v>
       </c>
       <c r="V169" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W169" s="2" t="s">
         <v>38</v>
@@ -18934,7 +18937,7 @@
     </row>
     <row r="170" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>24</v>
@@ -18943,46 +18946,46 @@
         <v>5</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F170" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="J170" s="11" t="s">
         <v>1389</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H170" s="2" t="s">
-        <v>1391</v>
-      </c>
-      <c r="I170" s="2" t="s">
-        <v>1879</v>
-      </c>
-      <c r="J170" s="11" t="s">
-        <v>1390</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="N170" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O170" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="P170" s="2" t="s">
         <v>1394</v>
       </c>
-      <c r="P170" s="2" t="s">
+      <c r="Q170" s="2" t="s">
         <v>1395</v>
-      </c>
-      <c r="Q170" s="2" t="s">
-        <v>1396</v>
       </c>
       <c r="R170" s="3" t="s">
         <v>35</v>
@@ -18997,7 +19000,7 @@
         <v>36</v>
       </c>
       <c r="V170" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W170" s="2" t="s">
         <v>38</v>
@@ -19005,7 +19008,7 @@
     </row>
     <row r="171" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>24</v>
@@ -19014,46 +19017,46 @@
         <v>5</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F171" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="G171" s="2" t="s">
         <v>1398</v>
       </c>
-      <c r="G171" s="2" t="s">
+      <c r="H171" s="2" t="s">
         <v>1399</v>
       </c>
-      <c r="H171" s="2" t="s">
+      <c r="I171" s="2" t="s">
         <v>1400</v>
       </c>
-      <c r="I171" s="2" t="s">
+      <c r="J171" s="2" t="s">
         <v>1401</v>
-      </c>
-      <c r="J171" s="2" t="s">
-        <v>1402</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="N171" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O171" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="P171" s="2" t="s">
         <v>1404</v>
       </c>
-      <c r="P171" s="2" t="s">
-        <v>1405</v>
-      </c>
       <c r="Q171" s="2" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="R171" s="3" t="s">
         <v>35</v>
@@ -19068,7 +19071,7 @@
         <v>36</v>
       </c>
       <c r="V171" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W171" s="2" t="s">
         <v>38</v>
@@ -19076,7 +19079,7 @@
     </row>
     <row r="172" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>24</v>
@@ -19085,46 +19088,46 @@
         <v>5</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F172" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H172" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="G172" s="2" t="s">
-        <v>1410</v>
-      </c>
-      <c r="H172" s="2" t="s">
+      <c r="I172" s="2" t="s">
         <v>1408</v>
       </c>
-      <c r="I172" s="2" t="s">
-        <v>1409</v>
-      </c>
       <c r="J172" s="11" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="N172" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O172" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="P172" s="2" t="s">
         <v>1412</v>
       </c>
-      <c r="P172" s="2" t="s">
+      <c r="Q172" s="2" t="s">
         <v>1413</v>
-      </c>
-      <c r="Q172" s="2" t="s">
-        <v>1414</v>
       </c>
       <c r="R172" s="3" t="s">
         <v>35</v>
@@ -19139,7 +19142,7 @@
         <v>36</v>
       </c>
       <c r="V172" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W172" s="2" t="s">
         <v>290</v>
@@ -19147,7 +19150,7 @@
     </row>
     <row r="173" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>24</v>
@@ -19156,22 +19159,22 @@
         <v>5</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F173" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H173" s="2" t="s">
         <v>1416</v>
       </c>
-      <c r="G173" s="2" t="s">
-        <v>1884</v>
-      </c>
-      <c r="H173" s="2" t="s">
+      <c r="I173" s="2" t="s">
         <v>1417</v>
-      </c>
-      <c r="I173" s="2" t="s">
-        <v>1418</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>381</v>
@@ -19180,22 +19183,22 @@
         <v>163</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="N173" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O173" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="P173" s="2" t="s">
         <v>1420</v>
       </c>
-      <c r="P173" s="2" t="s">
+      <c r="Q173" s="2" t="s">
         <v>1421</v>
-      </c>
-      <c r="Q173" s="2" t="s">
-        <v>1422</v>
       </c>
       <c r="R173" s="3" t="s">
         <v>35</v>
@@ -19210,7 +19213,7 @@
         <v>36</v>
       </c>
       <c r="V173" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W173" s="2" t="s">
         <v>38</v>
@@ -19218,7 +19221,7 @@
     </row>
     <row r="174" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>24</v>
@@ -19227,13 +19230,13 @@
         <v>5</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>458</v>
@@ -19242,31 +19245,31 @@
         <v>459</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="J174" s="11" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="N174" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O174" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="P174" s="2" t="s">
         <v>1428</v>
       </c>
-      <c r="P174" s="2" t="s">
+      <c r="Q174" s="2" t="s">
         <v>1429</v>
-      </c>
-      <c r="Q174" s="2" t="s">
-        <v>1430</v>
       </c>
       <c r="R174" s="3" t="s">
         <v>35</v>
@@ -19281,7 +19284,7 @@
         <v>36</v>
       </c>
       <c r="V174" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W174" s="2" t="s">
         <v>38</v>
@@ -19289,7 +19292,7 @@
     </row>
     <row r="175" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>24</v>
@@ -19298,46 +19301,46 @@
         <v>5</v>
       </c>
       <c r="D175" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E175" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F175" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G175" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="G175" s="2" t="s">
+      <c r="H175" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="J175" s="11" t="s">
         <v>1433</v>
-      </c>
-      <c r="H175" s="2" t="s">
-        <v>1888</v>
-      </c>
-      <c r="I175" s="2" t="s">
-        <v>1889</v>
-      </c>
-      <c r="J175" s="11" t="s">
-        <v>1434</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="N175" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O175" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="P175" s="2" t="s">
         <v>1436</v>
       </c>
-      <c r="P175" s="2" t="s">
+      <c r="Q175" s="2" t="s">
         <v>1437</v>
-      </c>
-      <c r="Q175" s="2" t="s">
-        <v>1438</v>
       </c>
       <c r="R175" s="3" t="s">
         <v>35</v>
@@ -19352,7 +19355,7 @@
         <v>36</v>
       </c>
       <c r="V175" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W175" s="2" t="s">
         <v>38</v>
@@ -19360,7 +19363,7 @@
     </row>
     <row r="176" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>24</v>
@@ -19369,46 +19372,46 @@
         <v>5</v>
       </c>
       <c r="D176" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E176" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E176" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F176" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="H176" s="2" t="s">
         <v>1440</v>
       </c>
-      <c r="G176" s="2" t="s">
+      <c r="I176" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="J176" s="11" t="s">
         <v>1891</v>
-      </c>
-      <c r="H176" s="2" t="s">
-        <v>1441</v>
-      </c>
-      <c r="I176" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="J176" s="11" t="s">
-        <v>1892</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="N176" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O176" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="P176" s="2" t="s">
         <v>1444</v>
       </c>
-      <c r="P176" s="2" t="s">
+      <c r="Q176" s="2" t="s">
         <v>1445</v>
-      </c>
-      <c r="Q176" s="2" t="s">
-        <v>1446</v>
       </c>
       <c r="R176" s="3" t="s">
         <v>35</v>
@@ -19423,7 +19426,7 @@
         <v>36</v>
       </c>
       <c r="V176" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W176" s="2" t="s">
         <v>38</v>
@@ -19431,7 +19434,7 @@
     </row>
     <row r="177" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>24</v>
@@ -19440,46 +19443,46 @@
         <v>5</v>
       </c>
       <c r="D177" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E177" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F177" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G177" s="2" t="s">
         <v>1448</v>
       </c>
-      <c r="G177" s="2" t="s">
+      <c r="H177" s="2" t="s">
         <v>1449</v>
       </c>
-      <c r="H177" s="2" t="s">
+      <c r="I177" s="2" t="s">
         <v>1450</v>
       </c>
-      <c r="I177" s="2" t="s">
+      <c r="J177" s="2" t="s">
         <v>1451</v>
-      </c>
-      <c r="J177" s="2" t="s">
-        <v>1452</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="N177" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O177" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="P177" s="2" t="s">
         <v>1454</v>
       </c>
-      <c r="P177" s="2" t="s">
+      <c r="Q177" s="2" t="s">
         <v>1455</v>
-      </c>
-      <c r="Q177" s="2" t="s">
-        <v>1456</v>
       </c>
       <c r="R177" s="3" t="s">
         <v>35</v>
@@ -19494,7 +19497,7 @@
         <v>36</v>
       </c>
       <c r="V177" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W177" s="2" t="s">
         <v>290</v>
@@ -19502,7 +19505,7 @@
     </row>
     <row r="178" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>24</v>
@@ -19511,46 +19514,46 @@
         <v>5</v>
       </c>
       <c r="D178" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E178" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F178" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="J178" s="11" t="s">
         <v>1458</v>
-      </c>
-      <c r="G178" s="2" t="s">
-        <v>1895</v>
-      </c>
-      <c r="H178" s="2" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I178" s="2" t="s">
-        <v>1461</v>
-      </c>
-      <c r="J178" s="11" t="s">
-        <v>1459</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="N178" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O178" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="P178" s="2" t="s">
         <v>1463</v>
       </c>
-      <c r="P178" s="2" t="s">
+      <c r="Q178" s="2" t="s">
         <v>1464</v>
-      </c>
-      <c r="Q178" s="2" t="s">
-        <v>1465</v>
       </c>
       <c r="R178" s="3" t="s">
         <v>35</v>
@@ -19565,7 +19568,7 @@
         <v>36</v>
       </c>
       <c r="V178" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W178" s="2" t="s">
         <v>38</v>
@@ -19573,7 +19576,7 @@
     </row>
     <row r="179" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>24</v>
@@ -19582,46 +19585,46 @@
         <v>5</v>
       </c>
       <c r="D179" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E179" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F179" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G179" s="2" t="s">
         <v>1467</v>
       </c>
-      <c r="G179" s="2" t="s">
+      <c r="H179" s="2" t="s">
         <v>1468</v>
       </c>
-      <c r="H179" s="2" t="s">
+      <c r="I179" s="2" t="s">
         <v>1469</v>
       </c>
-      <c r="I179" s="2" t="s">
-        <v>1470</v>
-      </c>
       <c r="J179" s="11" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="N179" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O179" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="P179" s="2" t="s">
         <v>1472</v>
       </c>
-      <c r="P179" s="2" t="s">
+      <c r="Q179" s="2" t="s">
         <v>1473</v>
-      </c>
-      <c r="Q179" s="2" t="s">
-        <v>1474</v>
       </c>
       <c r="R179" s="3" t="s">
         <v>35</v>
@@ -19636,7 +19639,7 @@
         <v>36</v>
       </c>
       <c r="V179" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W179" s="2" t="s">
         <v>38</v>
@@ -19644,7 +19647,7 @@
     </row>
     <row r="180" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>24</v>
@@ -19653,46 +19656,46 @@
         <v>5</v>
       </c>
       <c r="D180" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E180" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E180" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F180" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G180" s="2" t="s">
         <v>1476</v>
       </c>
-      <c r="G180" s="2" t="s">
+      <c r="H180" s="2" t="s">
         <v>1477</v>
       </c>
-      <c r="H180" s="2" t="s">
+      <c r="I180" s="2" t="s">
         <v>1478</v>
       </c>
-      <c r="I180" s="2" t="s">
-        <v>1479</v>
-      </c>
       <c r="J180" s="11" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="N180" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O180" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="P180" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="P180" s="2" t="s">
+      <c r="Q180" s="2" t="s">
         <v>1481</v>
-      </c>
-      <c r="Q180" s="2" t="s">
-        <v>1482</v>
       </c>
       <c r="R180" s="3" t="s">
         <v>35</v>
@@ -19707,7 +19710,7 @@
         <v>36</v>
       </c>
       <c r="V180" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W180" s="2" t="s">
         <v>290</v>
@@ -19715,7 +19718,7 @@
     </row>
     <row r="181" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>24</v>
@@ -19724,46 +19727,46 @@
         <v>5</v>
       </c>
       <c r="D181" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E181" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E181" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F181" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G181" s="2" t="s">
         <v>1484</v>
       </c>
-      <c r="G181" s="2" t="s">
+      <c r="H181" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="H181" s="2" t="s">
+      <c r="I181" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="I181" s="2" t="s">
+      <c r="J181" s="2" t="s">
         <v>1487</v>
-      </c>
-      <c r="J181" s="2" t="s">
-        <v>1488</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="N181" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O181" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="P181" s="2" t="s">
         <v>1490</v>
       </c>
-      <c r="P181" s="2" t="s">
+      <c r="Q181" s="2" t="s">
         <v>1491</v>
-      </c>
-      <c r="Q181" s="2" t="s">
-        <v>1492</v>
       </c>
       <c r="R181" s="3" t="s">
         <v>35</v>
@@ -19778,7 +19781,7 @@
         <v>36</v>
       </c>
       <c r="V181" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W181" s="2" t="s">
         <v>38</v>
@@ -19786,7 +19789,7 @@
     </row>
     <row r="182" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>24</v>
@@ -19795,46 +19798,46 @@
         <v>5</v>
       </c>
       <c r="D182" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E182" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E182" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F182" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="I182" s="2" t="s">
         <v>1494</v>
       </c>
-      <c r="G182" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="H182" s="2" t="s">
-        <v>1903</v>
-      </c>
-      <c r="I182" s="2" t="s">
-        <v>1495</v>
-      </c>
       <c r="J182" s="11" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="N182" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O182" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="P182" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="P182" s="2" t="s">
+      <c r="Q182" s="2" t="s">
         <v>1499</v>
-      </c>
-      <c r="Q182" s="2" t="s">
-        <v>1500</v>
       </c>
       <c r="R182" s="3" t="s">
         <v>35</v>
@@ -19849,7 +19852,7 @@
         <v>36</v>
       </c>
       <c r="V182" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W182" s="2" t="s">
         <v>38</v>
@@ -19857,7 +19860,7 @@
     </row>
     <row r="183" spans="1:23" ht="120" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>24</v>
@@ -19866,46 +19869,46 @@
         <v>5</v>
       </c>
       <c r="D183" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="E183" s="2" t="s">
-        <v>1307</v>
-      </c>
       <c r="F183" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G183" s="2" t="s">
         <v>1502</v>
       </c>
-      <c r="G183" s="2" t="s">
+      <c r="H183" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="I183" s="2" t="s">
         <v>1503</v>
       </c>
-      <c r="H183" s="2" t="s">
-        <v>1505</v>
-      </c>
-      <c r="I183" s="2" t="s">
-        <v>1504</v>
-      </c>
       <c r="J183" s="11" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="N183" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O183" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="P183" s="2" t="s">
         <v>1506</v>
       </c>
-      <c r="P183" s="2" t="s">
+      <c r="Q183" s="2" t="s">
         <v>1507</v>
-      </c>
-      <c r="Q183" s="2" t="s">
-        <v>1508</v>
       </c>
       <c r="R183" s="3" t="s">
         <v>35</v>
@@ -19920,7 +19923,7 @@
         <v>36</v>
       </c>
       <c r="V183" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W183" s="2" t="s">
         <v>38</v>
@@ -19928,7 +19931,7 @@
     </row>
     <row r="184" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>24</v>
@@ -19937,16 +19940,16 @@
         <v>5</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E184" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>1510</v>
       </c>
-      <c r="F184" s="2" t="s">
-        <v>1511</v>
-      </c>
       <c r="G184" s="2" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>460</v>
@@ -19961,22 +19964,22 @@
         <v>163</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="N184" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O184" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="P184" s="2" t="s">
         <v>1513</v>
       </c>
-      <c r="P184" s="2" t="s">
+      <c r="Q184" s="2" t="s">
         <v>1514</v>
-      </c>
-      <c r="Q184" s="2" t="s">
-        <v>1515</v>
       </c>
       <c r="R184" s="3" t="s">
         <v>35</v>
@@ -19991,7 +19994,7 @@
         <v>36</v>
       </c>
       <c r="V184" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W184" s="2" t="s">
         <v>38</v>
@@ -19999,7 +20002,7 @@
     </row>
     <row r="185" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>24</v>
@@ -20008,46 +20011,46 @@
         <v>5</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F185" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G185" s="2" t="s">
         <v>1517</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="H185" s="2" t="s">
         <v>1518</v>
       </c>
-      <c r="H185" s="2" t="s">
+      <c r="I185" s="2" t="s">
         <v>1519</v>
       </c>
-      <c r="I185" s="2" t="s">
+      <c r="J185" s="2" t="s">
         <v>1520</v>
-      </c>
-      <c r="J185" s="2" t="s">
-        <v>1521</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="N185" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O185" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="P185" s="2" t="s">
         <v>1523</v>
       </c>
-      <c r="P185" s="2" t="s">
+      <c r="Q185" s="2" t="s">
         <v>1524</v>
-      </c>
-      <c r="Q185" s="2" t="s">
-        <v>1525</v>
       </c>
       <c r="R185" s="3" t="s">
         <v>35</v>
@@ -20062,7 +20065,7 @@
         <v>36</v>
       </c>
       <c r="V185" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W185" s="2" t="s">
         <v>290</v>
@@ -20070,7 +20073,7 @@
     </row>
     <row r="186" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>24</v>
@@ -20079,34 +20082,34 @@
         <v>5</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F186" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G186" s="2" t="s">
         <v>1527</v>
       </c>
-      <c r="G186" s="2" t="s">
+      <c r="H186" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="I186" s="2" t="s">
         <v>1528</v>
       </c>
-      <c r="H186" s="2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="I186" s="2" t="s">
+      <c r="J186" s="2" t="s">
         <v>1529</v>
-      </c>
-      <c r="J186" s="2" t="s">
-        <v>1530</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="N186" s="3" t="s">
         <v>47</v>
@@ -20115,10 +20118,10 @@
         <v>339</v>
       </c>
       <c r="P186" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="Q186" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="R186" s="3" t="s">
         <v>35</v>
@@ -20133,7 +20136,7 @@
         <v>36</v>
       </c>
       <c r="V186" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W186" s="2" t="s">
         <v>38</v>
@@ -20141,7 +20144,7 @@
     </row>
     <row r="187" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>24</v>
@@ -20150,46 +20153,46 @@
         <v>5</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F187" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J187" s="11" t="s">
         <v>1534</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>1538</v>
-      </c>
-      <c r="H187" s="2" t="s">
-        <v>1536</v>
-      </c>
-      <c r="I187" s="2" t="s">
-        <v>1537</v>
-      </c>
-      <c r="J187" s="11" t="s">
-        <v>1535</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="N187" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O187" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="P187" s="2" t="s">
         <v>1540</v>
       </c>
-      <c r="P187" s="2" t="s">
+      <c r="Q187" s="2" t="s">
         <v>1541</v>
-      </c>
-      <c r="Q187" s="2" t="s">
-        <v>1542</v>
       </c>
       <c r="R187" s="3" t="s">
         <v>35</v>
@@ -20204,7 +20207,7 @@
         <v>36</v>
       </c>
       <c r="V187" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W187" s="2" t="s">
         <v>38</v>
@@ -20212,7 +20215,7 @@
     </row>
     <row r="188" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>24</v>
@@ -20221,46 +20224,46 @@
         <v>5</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F188" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G188" s="2" t="s">
         <v>1544</v>
       </c>
-      <c r="G188" s="2" t="s">
+      <c r="H188" s="2" t="s">
         <v>1545</v>
       </c>
-      <c r="H188" s="2" t="s">
+      <c r="I188" s="2" t="s">
         <v>1546</v>
       </c>
-      <c r="I188" s="2" t="s">
-        <v>1547</v>
-      </c>
       <c r="J188" s="11" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L188" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="M188" s="2" t="s">
         <v>1914</v>
-      </c>
-      <c r="M188" s="2" t="s">
-        <v>1915</v>
       </c>
       <c r="N188" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O188" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="P188" s="2" t="s">
         <v>1548</v>
       </c>
-      <c r="P188" s="2" t="s">
+      <c r="Q188" s="2" t="s">
         <v>1549</v>
-      </c>
-      <c r="Q188" s="2" t="s">
-        <v>1550</v>
       </c>
       <c r="R188" s="3" t="s">
         <v>35</v>
@@ -20275,7 +20278,7 @@
         <v>36</v>
       </c>
       <c r="V188" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W188" s="2" t="s">
         <v>38</v>
@@ -20283,7 +20286,7 @@
     </row>
     <row r="189" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>24</v>
@@ -20292,46 +20295,46 @@
         <v>5</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F189" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G189" s="2" t="s">
         <v>1553</v>
       </c>
-      <c r="G189" s="2" t="s">
+      <c r="H189" s="2" t="s">
         <v>1554</v>
       </c>
-      <c r="H189" s="2" t="s">
+      <c r="I189" s="2" t="s">
         <v>1555</v>
       </c>
-      <c r="I189" s="2" t="s">
+      <c r="J189" s="2" t="s">
         <v>1556</v>
-      </c>
-      <c r="J189" s="2" t="s">
-        <v>1557</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="N189" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O189" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="P189" s="2" t="s">
         <v>1559</v>
       </c>
-      <c r="P189" s="2" t="s">
+      <c r="Q189" s="2" t="s">
         <v>1560</v>
-      </c>
-      <c r="Q189" s="2" t="s">
-        <v>1561</v>
       </c>
       <c r="R189" s="3" t="s">
         <v>35</v>
@@ -20346,7 +20349,7 @@
         <v>36</v>
       </c>
       <c r="V189" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W189" s="2" t="s">
         <v>290</v>
@@ -20354,7 +20357,7 @@
     </row>
     <row r="190" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>24</v>
@@ -20363,46 +20366,46 @@
         <v>5</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F190" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G190" s="2" t="s">
         <v>1562</v>
       </c>
-      <c r="G190" s="2" t="s">
+      <c r="H190" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="I190" s="2" t="s">
         <v>1563</v>
       </c>
-      <c r="H190" s="2" t="s">
-        <v>1566</v>
-      </c>
-      <c r="I190" s="2" t="s">
+      <c r="J190" s="2" t="s">
         <v>1564</v>
-      </c>
-      <c r="J190" s="2" t="s">
-        <v>1565</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="N190" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O190" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="P190" s="2" t="s">
         <v>1568</v>
       </c>
-      <c r="P190" s="2" t="s">
+      <c r="Q190" s="2" t="s">
         <v>1569</v>
-      </c>
-      <c r="Q190" s="2" t="s">
-        <v>1570</v>
       </c>
       <c r="R190" s="3" t="s">
         <v>35</v>
@@ -20417,7 +20420,7 @@
         <v>36</v>
       </c>
       <c r="V190" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W190" s="2" t="s">
         <v>290</v>
@@ -20443,12 +20446,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21.6" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.35">
@@ -20456,12 +20459,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B5" s="8">
         <v>37</v>
@@ -20469,7 +20472,7 @@
     </row>
     <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B6" s="8">
         <v>46</v>
@@ -20477,7 +20480,7 @@
     </row>
     <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B7" s="8">
         <v>30</v>
@@ -20485,7 +20488,7 @@
     </row>
     <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B8" s="8">
         <v>47</v>
@@ -20493,7 +20496,7 @@
     </row>
     <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B9" s="8">
         <v>31</v>
@@ -20501,7 +20504,7 @@
     </row>
     <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B10" s="7">
         <v>191</v>
@@ -20509,15 +20512,15 @@
     </row>
     <row r="13" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>1581</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>1582</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.35">
@@ -20525,7 +20528,7 @@
         <v>0</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.35">
@@ -20533,15 +20536,15 @@
         <v>1</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>1585</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="60" x14ac:dyDescent="0.35">
@@ -20549,7 +20552,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.35">
@@ -20557,15 +20560,15 @@
         <v>5</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>1589</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.35">
@@ -20573,7 +20576,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.35">
@@ -20581,7 +20584,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="60" x14ac:dyDescent="0.35">
@@ -20589,7 +20592,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="75" x14ac:dyDescent="0.35">
@@ -20597,23 +20600,23 @@
         <v>13</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>1595</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>1597</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.35">
@@ -20621,7 +20624,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.35">
@@ -20629,7 +20632,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.35">
@@ -20637,12 +20640,12 @@
         <v>22</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="18" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B32" s="18"/>
     </row>

--- a/sources/BANQUE_OFFICIELLE_CSP.xlsx
+++ b/sources/BANQUE_OFFICIELLE_CSP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Documents\GitHub\Chatbot_civique2\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0752135-A356-4AEF-81B9-93CA34C34755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BF3D67-CA3D-4695-A8F2-8B943210E598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Banque_CSP_191" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="2016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="2015">
   <si>
     <t>ID</t>
   </si>
@@ -2303,6 +2303,9 @@
   </si>
   <si>
     <t>La Déclaration universelle des droits de l'homme de 1948.</t>
+  </si>
+  <si>
+    <t>La Convention européenne des droits de l'homme.</t>
   </si>
   <si>
     <t>Adoptée pendant la Révolution française, la DDHC affirme notamment la liberté, l'égalité devant la loi et les principaux droits des citoyens.</t>
@@ -6075,12 +6078,6 @@
   </si>
   <si>
     <t>Les services d'urgence sont destinés à prendre en charge les situations graves nécessitant des soins immédiats.</t>
-  </si>
-  <si>
-    <t>Le Code civil de 1804</t>
-  </si>
-  <si>
-    <t>La Convention européenne des droits de l'homme de 1908.</t>
   </si>
 </sst>
 </file>
@@ -7027,16 +7024,16 @@
         <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>29</v>
@@ -7045,7 +7042,7 @@
         <v>30</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>31</v>
@@ -7116,7 +7113,7 @@
         <v>46</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>47</v>
@@ -7246,10 +7243,10 @@
         <v>66</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>29</v>
@@ -7258,7 +7255,7 @@
         <v>69</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>31</v>
@@ -7311,7 +7308,7 @@
         <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>75</v>
@@ -7329,7 +7326,7 @@
         <v>78</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>47</v>
@@ -7385,13 +7382,13 @@
         <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>85</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>45</v>
@@ -7400,7 +7397,7 @@
         <v>86</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>47</v>
@@ -7471,7 +7468,7 @@
         <v>96</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>47</v>
@@ -7542,7 +7539,7 @@
         <v>106</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>31</v>
@@ -7613,7 +7610,7 @@
         <v>114</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>31</v>
@@ -7666,16 +7663,16 @@
         <v>119</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>45</v>
@@ -7684,7 +7681,7 @@
         <v>121</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>31</v>
@@ -7737,16 +7734,16 @@
         <v>126</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>1924</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>1923</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>29</v>
@@ -7755,7 +7752,7 @@
         <v>128</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>31</v>
@@ -7826,7 +7823,7 @@
         <v>137</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>47</v>
@@ -7959,7 +7956,7 @@
         <v>154</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>29</v>
@@ -7968,7 +7965,7 @@
         <v>155</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>47</v>
@@ -8027,7 +8024,7 @@
         <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>112</v>
@@ -8036,10 +8033,10 @@
         <v>163</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>31</v>
@@ -8095,13 +8092,13 @@
         <v>170</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>171</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>45</v>
@@ -8110,7 +8107,7 @@
         <v>172</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>47</v>
@@ -8166,13 +8163,13 @@
         <v>179</v>
       </c>
       <c r="H18" s="11" t="s">
+        <v>1629</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>1627</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>1628</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>1626</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>1627</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>58</v>
@@ -8234,10 +8231,10 @@
         <v>186</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>67</v>
@@ -8249,10 +8246,10 @@
         <v>45</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>31</v>
@@ -8323,7 +8320,7 @@
         <v>195</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>31</v>
@@ -8379,7 +8376,7 @@
         <v>201</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>202</v>
@@ -8456,7 +8453,7 @@
         <v>212</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>45</v>
@@ -8465,7 +8462,7 @@
         <v>213</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>31</v>
@@ -8518,7 +8515,7 @@
         <v>218</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>219</v>
@@ -8527,7 +8524,7 @@
         <v>220</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>29</v>
@@ -8536,7 +8533,7 @@
         <v>221</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>47</v>
@@ -8589,7 +8586,7 @@
         <v>226</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>228</v>
@@ -8604,10 +8601,10 @@
         <v>45</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>47</v>
@@ -8663,13 +8660,13 @@
         <v>236</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>237</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>58</v>
@@ -8678,7 +8675,7 @@
         <v>238</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>47</v>
@@ -8734,7 +8731,7 @@
         <v>244</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>245</v>
@@ -8746,10 +8743,10 @@
         <v>45</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>31</v>
@@ -8805,13 +8802,13 @@
         <v>249</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>250</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>45</v>
@@ -8879,7 +8876,7 @@
         <v>257</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>258</v>
@@ -8891,7 +8888,7 @@
         <v>259</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>31</v>
@@ -8953,7 +8950,7 @@
         <v>267</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>45</v>
@@ -8962,7 +8959,7 @@
         <v>268</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>31</v>
@@ -9033,7 +9030,7 @@
         <v>277</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>47</v>
@@ -9092,7 +9089,7 @@
         <v>283</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>285</v>
@@ -9104,7 +9101,7 @@
         <v>286</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>47</v>
@@ -9160,7 +9157,7 @@
         <v>92</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>93</v>
@@ -9175,7 +9172,7 @@
         <v>293</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>294</v>
@@ -9234,7 +9231,7 @@
         <v>300</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>302</v>
@@ -9299,25 +9296,25 @@
         <v>309</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>310</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>47</v>
@@ -9388,7 +9385,7 @@
         <v>320</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>47</v>
@@ -9459,7 +9456,7 @@
         <v>330</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>294</v>
@@ -9512,13 +9509,13 @@
         <v>335</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>336</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>337</v>
@@ -9530,7 +9527,7 @@
         <v>338</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>47</v>
@@ -9586,10 +9583,10 @@
         <v>344</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>345</v>
@@ -9601,7 +9598,7 @@
         <v>346</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>47</v>
@@ -9663,16 +9660,16 @@
         <v>354</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>31</v>
@@ -9681,10 +9678,10 @@
         <v>355</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="R39" s="3" t="s">
         <v>35</v>
@@ -9725,7 +9722,7 @@
         <v>358</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>359</v>
@@ -9734,7 +9731,7 @@
         <v>360</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>29</v>
@@ -9743,7 +9740,7 @@
         <v>361</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>31</v>
@@ -9796,13 +9793,13 @@
         <v>367</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>368</v>
@@ -9814,7 +9811,7 @@
         <v>369</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>294</v>
@@ -9823,10 +9820,10 @@
         <v>370</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>35</v>
@@ -9882,10 +9879,10 @@
         <v>45</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>47</v>
@@ -9938,7 +9935,7 @@
         <v>380</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>382</v>
@@ -9947,7 +9944,7 @@
         <v>383</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>45</v>
@@ -9956,7 +9953,7 @@
         <v>384</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>31</v>
@@ -10015,7 +10012,7 @@
         <v>391</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>392</v>
@@ -10024,10 +10021,10 @@
         <v>163</v>
       </c>
       <c r="L44" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="M44" s="2" t="s">
         <v>1675</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>1674</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>47</v>
@@ -10083,13 +10080,13 @@
         <v>399</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>58</v>
@@ -10098,7 +10095,7 @@
         <v>400</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>47</v>
@@ -10157,7 +10154,7 @@
         <v>407</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>408</v>
@@ -10169,7 +10166,7 @@
         <v>409</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>294</v>
@@ -10240,7 +10237,7 @@
         <v>418</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>47</v>
@@ -10293,7 +10290,7 @@
         <v>423</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>424</v>
@@ -10302,7 +10299,7 @@
         <v>425</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>45</v>
@@ -10311,7 +10308,7 @@
         <v>426</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>47</v>
@@ -10370,10 +10367,10 @@
         <v>433</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>29</v>
@@ -10382,7 +10379,7 @@
         <v>434</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>294</v>
@@ -10432,28 +10429,28 @@
         <v>350</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="I50" s="14" t="s">
         <v>439</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>58</v>
       </c>
       <c r="L50" s="14" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="M50" s="14" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="N50" s="15" t="s">
         <v>294</v>
@@ -10512,7 +10509,7 @@
         <v>352</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>446</v>
@@ -10583,19 +10580,19 @@
         <v>352</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>31</v>
@@ -10604,10 +10601,10 @@
         <v>455</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>35</v>
@@ -10666,7 +10663,7 @@
         <v>462</v>
       </c>
       <c r="M53" s="14" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="N53" s="15" t="s">
         <v>31</v>
@@ -10734,10 +10731,10 @@
         <v>29</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>47</v>
@@ -10746,10 +10743,10 @@
         <v>472</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>35</v>
@@ -10858,7 +10855,7 @@
         <v>350</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>481</v>
@@ -10876,10 +10873,10 @@
         <v>45</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>294</v>
@@ -10932,25 +10929,25 @@
         <v>485</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>47</v>
@@ -10959,10 +10956,10 @@
         <v>486</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>35</v>
@@ -11003,13 +11000,13 @@
         <v>488</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>490</v>
@@ -11021,7 +11018,7 @@
         <v>491</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>294</v>
@@ -11077,13 +11074,13 @@
         <v>498</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>497</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>58</v>
@@ -11092,7 +11089,7 @@
         <v>499</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>47</v>
@@ -11163,7 +11160,7 @@
         <v>508</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>294</v>
@@ -11234,7 +11231,7 @@
         <v>518</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>47</v>
@@ -11287,13 +11284,13 @@
         <v>523</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>524</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>525</v>
@@ -11302,10 +11299,10 @@
         <v>58</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>294</v>
@@ -11314,7 +11311,7 @@
         <v>526</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>527</v>
@@ -11361,13 +11358,13 @@
         <v>530</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>58</v>
@@ -11376,7 +11373,7 @@
         <v>531</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>47</v>
@@ -11429,10 +11426,10 @@
         <v>536</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>353</v>
@@ -11447,7 +11444,7 @@
         <v>537</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>47</v>
@@ -11500,7 +11497,7 @@
         <v>542</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>445</v>
@@ -11518,7 +11515,7 @@
         <v>545</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>47</v>
@@ -11571,7 +11568,7 @@
         <v>549</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>550</v>
@@ -11580,7 +11577,7 @@
         <v>417</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>29</v>
@@ -11589,7 +11586,7 @@
         <v>551</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>294</v>
@@ -11642,7 +11639,7 @@
         <v>556</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>416</v>
@@ -11660,7 +11657,7 @@
         <v>557</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>47</v>
@@ -11722,16 +11719,16 @@
         <v>564</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>31</v>
@@ -11740,10 +11737,10 @@
         <v>355</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="R68" s="3" t="s">
         <v>35</v>
@@ -11787,13 +11784,13 @@
         <v>570</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>569</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>58</v>
@@ -11802,7 +11799,7 @@
         <v>571</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>47</v>
@@ -11873,7 +11870,7 @@
         <v>580</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>47</v>
@@ -11935,7 +11932,7 @@
         <v>445</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>45</v>
@@ -11944,7 +11941,7 @@
         <v>586</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>47</v>
@@ -11997,13 +11994,13 @@
         <v>591</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>592</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>593</v>
@@ -12012,10 +12009,10 @@
         <v>163</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>47</v>
@@ -12024,7 +12021,7 @@
         <v>370</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="Q72" s="2" t="s">
         <v>594</v>
@@ -12083,10 +12080,10 @@
         <v>29</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>294</v>
@@ -12139,7 +12136,7 @@
         <v>603</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>604</v>
@@ -12148,16 +12145,16 @@
         <v>605</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>294</v>
@@ -12219,7 +12216,7 @@
         <v>103</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>45</v>
@@ -12228,7 +12225,7 @@
         <v>610</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>31</v>
@@ -12299,7 +12296,7 @@
         <v>621</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>294</v>
@@ -12370,7 +12367,7 @@
         <v>631</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>294</v>
@@ -12429,10 +12426,10 @@
         <v>490</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>29</v>
@@ -12441,7 +12438,7 @@
         <v>636</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>294</v>
@@ -12503,7 +12500,7 @@
         <v>642</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>29</v>
@@ -12512,7 +12509,7 @@
         <v>644</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>294</v>
@@ -12583,7 +12580,7 @@
         <v>654</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>31</v>
@@ -12654,7 +12651,7 @@
         <v>664</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>31</v>
@@ -12710,10 +12707,10 @@
         <v>352</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>354</v>
@@ -12725,7 +12722,7 @@
         <v>670</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>47</v>
@@ -12787,7 +12784,7 @@
         <v>191</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>29</v>
@@ -12796,7 +12793,7 @@
         <v>675</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>294</v>
@@ -12867,7 +12864,7 @@
         <v>687</v>
       </c>
       <c r="M84" s="14" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="N84" s="15" t="s">
         <v>47</v>
@@ -12926,10 +12923,10 @@
         <v>686</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>45</v>
@@ -12938,7 +12935,7 @@
         <v>695</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>47</v>
@@ -13009,7 +13006,7 @@
         <v>705</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>294</v>
@@ -13080,7 +13077,7 @@
         <v>712</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>31</v>
@@ -13151,7 +13148,7 @@
         <v>722</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="N88" s="3" t="s">
         <v>294</v>
@@ -13222,7 +13219,7 @@
         <v>731</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>47</v>
@@ -13284,7 +13281,7 @@
         <v>740</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>29</v>
@@ -13293,7 +13290,7 @@
         <v>741</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="N90" s="3" t="s">
         <v>31</v>
@@ -13420,34 +13417,34 @@
         <v>757</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>2014</v>
+        <v>686</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>694</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>2015</v>
+        <v>758</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="N92" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="R92" s="3" t="s">
         <v>35</v>
@@ -13470,7 +13467,7 @@
     </row>
     <row r="93" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
@@ -13485,40 +13482,40 @@
         <v>681</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>684</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="N93" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="R93" s="3" t="s">
         <v>35</v>
@@ -13541,7 +13538,7 @@
     </row>
     <row r="94" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>24</v>
@@ -13556,7 +13553,7 @@
         <v>736</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>229</v>
@@ -13574,22 +13571,22 @@
         <v>45</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>35</v>
@@ -13612,7 +13609,7 @@
     </row>
     <row r="95" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>24</v>
@@ -13624,43 +13621,43 @@
         <v>680</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="R95" s="3" t="s">
         <v>35</v>
@@ -13683,7 +13680,7 @@
     </row>
     <row r="96" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>24</v>
@@ -13695,19 +13692,19 @@
         <v>680</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>381</v>
@@ -13716,22 +13713,22 @@
         <v>163</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="R96" s="3" t="s">
         <v>35</v>
@@ -13754,7 +13751,7 @@
     </row>
     <row r="97" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>24</v>
@@ -13769,40 +13766,40 @@
         <v>681</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="R97" s="3" t="s">
         <v>35</v>
@@ -13825,7 +13822,7 @@
     </row>
     <row r="98" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>24</v>
@@ -13840,40 +13837,40 @@
         <v>736</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="R98" s="3" t="s">
         <v>35</v>
@@ -13896,7 +13893,7 @@
     </row>
     <row r="99" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>24</v>
@@ -13908,43 +13905,43 @@
         <v>680</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="R99" s="3" t="s">
         <v>35</v>
@@ -13967,7 +13964,7 @@
     </row>
     <row r="100" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>24</v>
@@ -13979,19 +13976,19 @@
         <v>680</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>381</v>
@@ -14000,22 +13997,22 @@
         <v>163</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>35</v>
@@ -14038,7 +14035,7 @@
     </row>
     <row r="101" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>24</v>
@@ -14050,43 +14047,43 @@
         <v>680</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>35</v>
@@ -14109,7 +14106,7 @@
     </row>
     <row r="102" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>24</v>
@@ -14124,40 +14121,40 @@
         <v>736</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>35</v>
@@ -14180,7 +14177,7 @@
     </row>
     <row r="103" spans="1:23" ht="105" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>24</v>
@@ -14192,43 +14189,43 @@
         <v>680</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="N103" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="R103" s="3" t="s">
         <v>35</v>
@@ -14251,7 +14248,7 @@
     </row>
     <row r="104" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>24</v>
@@ -14263,43 +14260,43 @@
         <v>680</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G104" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="I104" s="11" t="s">
         <v>857</v>
       </c>
-      <c r="I104" s="11" t="s">
-        <v>856</v>
-      </c>
       <c r="J104" s="2" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="N104" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="R104" s="3" t="s">
         <v>35</v>
@@ -14322,7 +14319,7 @@
     </row>
     <row r="105" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>24</v>
@@ -14334,43 +14331,43 @@
         <v>680</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="N105" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="R105" s="3" t="s">
         <v>35</v>
@@ -14393,7 +14390,7 @@
     </row>
     <row r="106" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>24</v>
@@ -14405,43 +14402,43 @@
         <v>680</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>398</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="N106" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="R106" s="3" t="s">
         <v>35</v>
@@ -14464,7 +14461,7 @@
     </row>
     <row r="107" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>24</v>
@@ -14476,43 +14473,43 @@
         <v>680</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="I107" s="11" t="s">
         <v>398</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="N107" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="R107" s="3" t="s">
         <v>35</v>
@@ -14535,7 +14532,7 @@
     </row>
     <row r="108" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>24</v>
@@ -14547,43 +14544,43 @@
         <v>680</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="N108" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="R108" s="3" t="s">
         <v>35</v>
@@ -14606,7 +14603,7 @@
     </row>
     <row r="109" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>24</v>
@@ -14618,43 +14615,43 @@
         <v>680</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="G109" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="I109" s="11" t="s">
+        <v>1766</v>
+      </c>
+      <c r="J109" s="2" t="s">
         <v>1767</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="I109" s="11" t="s">
-        <v>1765</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>1766</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="N109" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="R109" s="3" t="s">
         <v>35</v>
@@ -14677,7 +14674,7 @@
     </row>
     <row r="110" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>24</v>
@@ -14689,43 +14686,43 @@
         <v>680</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="N110" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="R110" s="3" t="s">
         <v>35</v>
@@ -14748,7 +14745,7 @@
     </row>
     <row r="111" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>24</v>
@@ -14760,43 +14757,43 @@
         <v>680</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G111" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>1773</v>
       </c>
-      <c r="H111" s="2" t="s">
+      <c r="I111" s="11" t="s">
         <v>1772</v>
       </c>
-      <c r="I111" s="11" t="s">
-        <v>1771</v>
-      </c>
       <c r="J111" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="N111" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="R111" s="3" t="s">
         <v>35</v>
@@ -14819,7 +14816,7 @@
     </row>
     <row r="112" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>24</v>
@@ -14831,43 +14828,43 @@
         <v>680</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H112" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I112" s="11" t="s">
         <v>1776</v>
       </c>
-      <c r="I112" s="11" t="s">
-        <v>1775</v>
-      </c>
       <c r="J112" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="R112" s="3" t="s">
         <v>35</v>
@@ -14890,7 +14887,7 @@
     </row>
     <row r="113" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>24</v>
@@ -14902,43 +14899,43 @@
         <v>680</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="N113" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="R113" s="3" t="s">
         <v>35</v>
@@ -14961,7 +14958,7 @@
     </row>
     <row r="114" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>24</v>
@@ -14970,34 +14967,34 @@
         <v>4</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>92</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="N114" s="3" t="s">
         <v>31</v>
@@ -15006,10 +15003,10 @@
         <v>713</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="R114" s="3" t="s">
         <v>35</v>
@@ -15024,7 +15021,7 @@
         <v>36</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W114" s="2" t="s">
         <v>38</v>
@@ -15032,7 +15029,7 @@
     </row>
     <row r="115" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>24</v>
@@ -15041,46 +15038,46 @@
         <v>4</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="N115" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="R115" s="3" t="s">
         <v>35</v>
@@ -15095,7 +15092,7 @@
         <v>36</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W115" s="2" t="s">
         <v>38</v>
@@ -15103,7 +15100,7 @@
     </row>
     <row r="116" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>24</v>
@@ -15112,46 +15109,46 @@
         <v>4</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="N116" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="R116" s="3" t="s">
         <v>35</v>
@@ -15166,7 +15163,7 @@
         <v>36</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W116" s="2" t="s">
         <v>290</v>
@@ -15174,7 +15171,7 @@
     </row>
     <row r="117" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>24</v>
@@ -15183,34 +15180,34 @@
         <v>4</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="N117" s="3" t="s">
         <v>31</v>
@@ -15219,10 +15216,10 @@
         <v>611</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="R117" s="3" t="s">
         <v>35</v>
@@ -15237,7 +15234,7 @@
         <v>36</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W117" s="2" t="s">
         <v>38</v>
@@ -15245,7 +15242,7 @@
     </row>
     <row r="118" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>24</v>
@@ -15254,46 +15251,46 @@
         <v>4</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="N118" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="Q118" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="R118" s="3" t="s">
         <v>35</v>
@@ -15308,7 +15305,7 @@
         <v>36</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W118" s="2" t="s">
         <v>38</v>
@@ -15316,7 +15313,7 @@
     </row>
     <row r="119" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>24</v>
@@ -15325,46 +15322,46 @@
         <v>4</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G119" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="H119" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="H119" s="2" t="s">
-        <v>984</v>
-      </c>
       <c r="I119" s="11" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="N119" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="R119" s="3" t="s">
         <v>35</v>
@@ -15379,7 +15376,7 @@
         <v>36</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W119" s="2" t="s">
         <v>38</v>
@@ -15387,7 +15384,7 @@
     </row>
     <row r="120" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>24</v>
@@ -15396,46 +15393,46 @@
         <v>4</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="N120" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="Q120" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="R120" s="3" t="s">
         <v>35</v>
@@ -15450,7 +15447,7 @@
         <v>36</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W120" s="2" t="s">
         <v>38</v>
@@ -15458,7 +15455,7 @@
     </row>
     <row r="121" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>24</v>
@@ -15467,46 +15464,46 @@
         <v>4</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="N121" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="Q121" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="R121" s="3" t="s">
         <v>35</v>
@@ -15521,7 +15518,7 @@
         <v>36</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W121" s="2" t="s">
         <v>38</v>
@@ -15529,7 +15526,7 @@
     </row>
     <row r="122" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>24</v>
@@ -15538,46 +15535,46 @@
         <v>4</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="N122" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="Q122" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="R122" s="3" t="s">
         <v>35</v>
@@ -15592,7 +15589,7 @@
         <v>36</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W122" s="2" t="s">
         <v>38</v>
@@ -15600,7 +15597,7 @@
     </row>
     <row r="123" spans="1:23" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.3">
       <c r="A123" s="14" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>24</v>
@@ -15609,46 +15606,46 @@
         <v>4</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F123" s="14" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H123" s="14" t="s">
         <v>93</v>
       </c>
       <c r="I123" s="14" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="K123" s="16" t="s">
         <v>163</v>
       </c>
       <c r="L123" s="14" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M123" s="14" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="N123" s="15" t="s">
         <v>294</v>
       </c>
       <c r="O123" s="14" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="R123" s="15" t="s">
         <v>35</v>
@@ -15663,7 +15660,7 @@
         <v>36</v>
       </c>
       <c r="V123" s="14" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W123" s="14" t="s">
         <v>38</v>
@@ -15671,7 +15668,7 @@
     </row>
     <row r="124" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>24</v>
@@ -15680,46 +15677,46 @@
         <v>4</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="N124" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="Q124" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="R124" s="3" t="s">
         <v>35</v>
@@ -15734,7 +15731,7 @@
         <v>36</v>
       </c>
       <c r="V124" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W124" s="2" t="s">
         <v>38</v>
@@ -15742,7 +15739,7 @@
     </row>
     <row r="125" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>24</v>
@@ -15751,46 +15748,46 @@
         <v>4</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="N125" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="P125" s="2" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="Q125" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="R125" s="3" t="s">
         <v>35</v>
@@ -15805,7 +15802,7 @@
         <v>36</v>
       </c>
       <c r="V125" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W125" s="2" t="s">
         <v>38</v>
@@ -15813,7 +15810,7 @@
     </row>
     <row r="126" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>24</v>
@@ -15822,34 +15819,34 @@
         <v>4</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="J126" s="11" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="N126" s="3" t="s">
         <v>47</v>
@@ -15858,10 +15855,10 @@
         <v>713</v>
       </c>
       <c r="P126" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="Q126" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="R126" s="3" t="s">
         <v>35</v>
@@ -15876,7 +15873,7 @@
         <v>36</v>
       </c>
       <c r="V126" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W126" s="2" t="s">
         <v>38</v>
@@ -15884,7 +15881,7 @@
     </row>
     <row r="127" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>24</v>
@@ -15893,16 +15890,16 @@
         <v>4</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>94</v>
@@ -15911,28 +15908,28 @@
         <v>93</v>
       </c>
       <c r="J127" s="11" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="N127" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="P127" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="Q127" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="R127" s="3" t="s">
         <v>35</v>
@@ -15947,7 +15944,7 @@
         <v>36</v>
       </c>
       <c r="V127" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W127" s="2" t="s">
         <v>38</v>
@@ -15955,7 +15952,7 @@
     </row>
     <row r="128" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>24</v>
@@ -15964,46 +15961,46 @@
         <v>4</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="N128" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="Q128" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="R128" s="3" t="s">
         <v>35</v>
@@ -16018,7 +16015,7 @@
         <v>36</v>
       </c>
       <c r="V128" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W128" s="2" t="s">
         <v>38</v>
@@ -16026,7 +16023,7 @@
     </row>
     <row r="129" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>24</v>
@@ -16035,46 +16032,46 @@
         <v>4</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H129" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I129" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="I129" s="2" t="s">
+      <c r="J129" s="11" t="s">
         <v>1067</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>1066</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="N129" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="P129" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="Q129" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="R129" s="3" t="s">
         <v>35</v>
@@ -16089,7 +16086,7 @@
         <v>36</v>
       </c>
       <c r="V129" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W129" s="2" t="s">
         <v>38</v>
@@ -16097,7 +16094,7 @@
     </row>
     <row r="130" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>24</v>
@@ -16106,46 +16103,46 @@
         <v>4</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="N130" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="P130" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Q130" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="R130" s="3" t="s">
         <v>35</v>
@@ -16160,7 +16157,7 @@
         <v>36</v>
       </c>
       <c r="V130" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W130" s="2" t="s">
         <v>38</v>
@@ -16168,7 +16165,7 @@
     </row>
     <row r="131" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>24</v>
@@ -16177,46 +16174,46 @@
         <v>4</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="N131" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="P131" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="Q131" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="R131" s="3" t="s">
         <v>35</v>
@@ -16231,7 +16228,7 @@
         <v>36</v>
       </c>
       <c r="V131" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W131" s="2" t="s">
         <v>38</v>
@@ -16239,7 +16236,7 @@
     </row>
     <row r="132" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>24</v>
@@ -16248,46 +16245,46 @@
         <v>4</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G132" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I132" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="H132" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>1087</v>
-      </c>
       <c r="J132" s="11" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="N132" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="P132" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="Q132" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="R132" s="3" t="s">
         <v>35</v>
@@ -16302,7 +16299,7 @@
         <v>36</v>
       </c>
       <c r="V132" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W132" s="2" t="s">
         <v>38</v>
@@ -16310,7 +16307,7 @@
     </row>
     <row r="133" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>24</v>
@@ -16319,46 +16316,46 @@
         <v>4</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="N133" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="P133" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="Q133" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="R133" s="3" t="s">
         <v>35</v>
@@ -16373,7 +16370,7 @@
         <v>36</v>
       </c>
       <c r="V133" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W133" s="2" t="s">
         <v>38</v>
@@ -16381,7 +16378,7 @@
     </row>
     <row r="134" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>24</v>
@@ -16390,46 +16387,46 @@
         <v>4</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="I134" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="J134" s="11" t="s">
         <v>1106</v>
-      </c>
-      <c r="J134" s="11" t="s">
-        <v>1105</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="N134" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="P134" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="Q134" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="R134" s="3" t="s">
         <v>35</v>
@@ -16444,7 +16441,7 @@
         <v>36</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W134" s="2" t="s">
         <v>38</v>
@@ -16452,7 +16449,7 @@
     </row>
     <row r="135" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>24</v>
@@ -16461,46 +16458,46 @@
         <v>4</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L135" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="N135" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="P135" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="Q135" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="R135" s="3" t="s">
         <v>35</v>
@@ -16515,7 +16512,7 @@
         <v>36</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W135" s="2" t="s">
         <v>290</v>
@@ -16523,7 +16520,7 @@
     </row>
     <row r="136" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>24</v>
@@ -16532,46 +16529,46 @@
         <v>4</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H136" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I136" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="I136" s="2" t="s">
-        <v>1124</v>
-      </c>
       <c r="J136" s="2" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L136" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="N136" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O136" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="Q136" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="R136" s="3" t="s">
         <v>35</v>
@@ -16586,7 +16583,7 @@
         <v>36</v>
       </c>
       <c r="V136" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W136" s="2" t="s">
         <v>38</v>
@@ -16594,7 +16591,7 @@
     </row>
     <row r="137" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>24</v>
@@ -16603,46 +16600,46 @@
         <v>4</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="N137" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="P137" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="Q137" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="R137" s="3" t="s">
         <v>35</v>
@@ -16657,7 +16654,7 @@
         <v>36</v>
       </c>
       <c r="V137" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W137" s="2" t="s">
         <v>38</v>
@@ -16665,7 +16662,7 @@
     </row>
     <row r="138" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>24</v>
@@ -16674,46 +16671,46 @@
         <v>4</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G138" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I138" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="H138" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="I138" s="2" t="s">
-        <v>1139</v>
-      </c>
       <c r="J138" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="N138" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="P138" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="Q138" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="R138" s="3" t="s">
         <v>35</v>
@@ -16728,7 +16725,7 @@
         <v>36</v>
       </c>
       <c r="V138" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W138" s="2" t="s">
         <v>38</v>
@@ -16736,7 +16733,7 @@
     </row>
     <row r="139" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>24</v>
@@ -16745,46 +16742,46 @@
         <v>4</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="J139" s="11" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L139" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="N139" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="P139" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="Q139" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="R139" s="3" t="s">
         <v>35</v>
@@ -16799,7 +16796,7 @@
         <v>36</v>
       </c>
       <c r="V139" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W139" s="2" t="s">
         <v>38</v>
@@ -16807,7 +16804,7 @@
     </row>
     <row r="140" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>24</v>
@@ -16816,46 +16813,46 @@
         <v>4</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="N140" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="P140" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="Q140" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="R140" s="3" t="s">
         <v>35</v>
@@ -16870,7 +16867,7 @@
         <v>36</v>
       </c>
       <c r="V140" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W140" s="2" t="s">
         <v>290</v>
@@ -16878,7 +16875,7 @@
     </row>
     <row r="141" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>24</v>
@@ -16887,13 +16884,13 @@
         <v>4</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>569</v>
@@ -16902,31 +16899,31 @@
         <v>568</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="J141" s="11" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="N141" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="P141" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="Q141" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="R141" s="3" t="s">
         <v>35</v>
@@ -16941,7 +16938,7 @@
         <v>36</v>
       </c>
       <c r="V141" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W141" s="2" t="s">
         <v>38</v>
@@ -16949,7 +16946,7 @@
     </row>
     <row r="142" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>24</v>
@@ -16958,46 +16955,46 @@
         <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J142" s="11" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="N142" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O142" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="P142" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="Q142" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="R142" s="3" t="s">
         <v>35</v>
@@ -17012,7 +17009,7 @@
         <v>36</v>
       </c>
       <c r="V142" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W142" s="2" t="s">
         <v>38</v>
@@ -17020,7 +17017,7 @@
     </row>
     <row r="143" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>24</v>
@@ -17029,46 +17026,46 @@
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="N143" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="P143" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="Q143" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="R143" s="3" t="s">
         <v>35</v>
@@ -17083,7 +17080,7 @@
         <v>36</v>
       </c>
       <c r="V143" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W143" s="2" t="s">
         <v>38</v>
@@ -17091,7 +17088,7 @@
     </row>
     <row r="144" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>24</v>
@@ -17100,46 +17097,46 @@
         <v>4</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L144" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="N144" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="P144" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="Q144" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="R144" s="3" t="s">
         <v>35</v>
@@ -17154,7 +17151,7 @@
         <v>36</v>
       </c>
       <c r="V144" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W144" s="2" t="s">
         <v>290</v>
@@ -17162,7 +17159,7 @@
     </row>
     <row r="145" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>24</v>
@@ -17171,46 +17168,46 @@
         <v>4</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H145" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I145" s="11" t="s">
         <v>1195</v>
       </c>
-      <c r="I145" s="11" t="s">
-        <v>1194</v>
-      </c>
       <c r="J145" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="N145" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="P145" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="Q145" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="R145" s="3" t="s">
         <v>35</v>
@@ -17225,7 +17222,7 @@
         <v>36</v>
       </c>
       <c r="V145" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W145" s="2" t="s">
         <v>290</v>
@@ -17233,7 +17230,7 @@
     </row>
     <row r="146" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>24</v>
@@ -17242,46 +17239,46 @@
         <v>4</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="G146" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H146" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="H146" s="2" t="s">
-        <v>1203</v>
-      </c>
       <c r="I146" s="11" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="J146" s="11" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L146" s="2" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="N146" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O146" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="P146" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="Q146" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="R146" s="3" t="s">
         <v>35</v>
@@ -17296,7 +17293,7 @@
         <v>36</v>
       </c>
       <c r="V146" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W146" s="2" t="s">
         <v>38</v>
@@ -17304,7 +17301,7 @@
     </row>
     <row r="147" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>24</v>
@@ -17313,46 +17310,46 @@
         <v>4</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G147" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="H147" s="2" t="s">
         <v>1832</v>
       </c>
-      <c r="H147" s="2" t="s">
+      <c r="I147" s="2" t="s">
         <v>1831</v>
       </c>
-      <c r="I147" s="2" t="s">
+      <c r="J147" s="11" t="s">
         <v>1830</v>
-      </c>
-      <c r="J147" s="11" t="s">
-        <v>1829</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L147" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="N147" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="P147" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="Q147" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="R147" s="3" t="s">
         <v>35</v>
@@ -17367,7 +17364,7 @@
         <v>36</v>
       </c>
       <c r="V147" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W147" s="2" t="s">
         <v>38</v>
@@ -17375,7 +17372,7 @@
     </row>
     <row r="148" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>24</v>
@@ -17384,46 +17381,46 @@
         <v>4</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="J148" s="11" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L148" s="2" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="N148" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="P148" s="2" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="Q148" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="R148" s="3" t="s">
         <v>35</v>
@@ -17438,7 +17435,7 @@
         <v>36</v>
       </c>
       <c r="V148" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W148" s="2" t="s">
         <v>38</v>
@@ -17446,7 +17443,7 @@
     </row>
     <row r="149" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>24</v>
@@ -17455,46 +17452,46 @@
         <v>4</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="J149" s="11" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L149" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="M149" s="2" t="s">
         <v>1839</v>
-      </c>
-      <c r="M149" s="2" t="s">
-        <v>1838</v>
       </c>
       <c r="N149" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="P149" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="Q149" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="R149" s="3" t="s">
         <v>35</v>
@@ -17509,7 +17506,7 @@
         <v>36</v>
       </c>
       <c r="V149" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W149" s="2" t="s">
         <v>38</v>
@@ -17517,7 +17514,7 @@
     </row>
     <row r="150" spans="1:23" ht="120" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>24</v>
@@ -17526,46 +17523,46 @@
         <v>4</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="G150" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H150" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="H150" s="2" t="s">
-        <v>1226</v>
-      </c>
       <c r="I150" s="2" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="J150" s="11" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L150" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="M150" s="2" t="s">
         <v>1842</v>
-      </c>
-      <c r="M150" s="2" t="s">
-        <v>1841</v>
       </c>
       <c r="N150" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="P150" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="Q150" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="R150" s="3" t="s">
         <v>35</v>
@@ -17580,7 +17577,7 @@
         <v>36</v>
       </c>
       <c r="V150" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W150" s="2" t="s">
         <v>38</v>
@@ -17588,7 +17585,7 @@
     </row>
     <row r="151" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>24</v>
@@ -17597,46 +17594,46 @@
         <v>4</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="N151" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="P151" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="Q151" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="R151" s="3" t="s">
         <v>35</v>
@@ -17651,7 +17648,7 @@
         <v>36</v>
       </c>
       <c r="V151" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W151" s="2" t="s">
         <v>38</v>
@@ -17659,7 +17656,7 @@
     </row>
     <row r="152" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>24</v>
@@ -17668,46 +17665,46 @@
         <v>4</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L152" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="M152" s="2" t="s">
         <v>1846</v>
-      </c>
-      <c r="M152" s="2" t="s">
-        <v>1845</v>
       </c>
       <c r="N152" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O152" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="P152" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="Q152" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="R152" s="3" t="s">
         <v>35</v>
@@ -17722,7 +17719,7 @@
         <v>36</v>
       </c>
       <c r="V152" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W152" s="2" t="s">
         <v>38</v>
@@ -17730,7 +17727,7 @@
     </row>
     <row r="153" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>24</v>
@@ -17739,46 +17736,46 @@
         <v>4</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="J153" s="11" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L153" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="M153" s="2" t="s">
         <v>1848</v>
-      </c>
-      <c r="M153" s="2" t="s">
-        <v>1847</v>
       </c>
       <c r="N153" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O153" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="P153" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="R153" s="3" t="s">
         <v>35</v>
@@ -17793,7 +17790,7 @@
         <v>36</v>
       </c>
       <c r="V153" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W153" s="2" t="s">
         <v>38</v>
@@ -17801,7 +17798,7 @@
     </row>
     <row r="154" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>24</v>
@@ -17810,46 +17807,46 @@
         <v>4</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="N154" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="P154" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="Q154" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="R154" s="3" t="s">
         <v>35</v>
@@ -17864,7 +17861,7 @@
         <v>36</v>
       </c>
       <c r="V154" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W154" s="2" t="s">
         <v>38</v>
@@ -17872,7 +17869,7 @@
     </row>
     <row r="155" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>24</v>
@@ -17881,46 +17878,46 @@
         <v>4</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="N155" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="P155" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="Q155" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="R155" s="3" t="s">
         <v>35</v>
@@ -17935,7 +17932,7 @@
         <v>36</v>
       </c>
       <c r="V155" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W155" s="2" t="s">
         <v>290</v>
@@ -17943,7 +17940,7 @@
     </row>
     <row r="156" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>24</v>
@@ -17952,46 +17949,46 @@
         <v>4</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="N156" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O156" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="P156" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="Q156" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="R156" s="3" t="s">
         <v>35</v>
@@ -18006,7 +18003,7 @@
         <v>36</v>
       </c>
       <c r="V156" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W156" s="2" t="s">
         <v>38</v>
@@ -18014,7 +18011,7 @@
     </row>
     <row r="157" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>24</v>
@@ -18023,46 +18020,46 @@
         <v>4</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="N157" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="P157" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="Q157" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="R157" s="3" t="s">
         <v>35</v>
@@ -18077,7 +18074,7 @@
         <v>36</v>
       </c>
       <c r="V157" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W157" s="2" t="s">
         <v>38</v>
@@ -18085,7 +18082,7 @@
     </row>
     <row r="158" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>24</v>
@@ -18094,46 +18091,46 @@
         <v>4</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="N158" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O158" s="2" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="P158" s="2" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="Q158" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="R158" s="3" t="s">
         <v>35</v>
@@ -18148,7 +18145,7 @@
         <v>36</v>
       </c>
       <c r="V158" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W158" s="2" t="s">
         <v>290</v>
@@ -18156,7 +18153,7 @@
     </row>
     <row r="159" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>24</v>
@@ -18165,46 +18162,46 @@
         <v>4</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L159" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="N159" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O159" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="P159" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="Q159" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="R159" s="3" t="s">
         <v>35</v>
@@ -18219,7 +18216,7 @@
         <v>36</v>
       </c>
       <c r="V159" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W159" s="2" t="s">
         <v>38</v>
@@ -18227,7 +18224,7 @@
     </row>
     <row r="160" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>24</v>
@@ -18236,16 +18233,16 @@
         <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>194</v>
@@ -18254,28 +18251,28 @@
         <v>191</v>
       </c>
       <c r="J160" s="11" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="N160" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O160" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="P160" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="Q160" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="R160" s="3" t="s">
         <v>35</v>
@@ -18290,7 +18287,7 @@
         <v>36</v>
       </c>
       <c r="V160" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="W160" s="2" t="s">
         <v>38</v>
@@ -18298,7 +18295,7 @@
     </row>
     <row r="161" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>24</v>
@@ -18307,46 +18304,46 @@
         <v>5</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>569</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="N161" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O161" s="2" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="P161" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="Q161" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="R161" s="3" t="s">
         <v>35</v>
@@ -18361,7 +18358,7 @@
         <v>36</v>
       </c>
       <c r="V161" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W161" s="2" t="s">
         <v>38</v>
@@ -18369,7 +18366,7 @@
     </row>
     <row r="162" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>24</v>
@@ -18378,46 +18375,46 @@
         <v>5</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="G162" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H162" s="2" t="s">
         <v>1309</v>
-      </c>
-      <c r="H162" s="2" t="s">
-        <v>1308</v>
       </c>
       <c r="I162" s="2" t="s">
         <v>569</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="N162" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O162" s="2" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="P162" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q162" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="R162" s="3" t="s">
         <v>35</v>
@@ -18432,7 +18429,7 @@
         <v>36</v>
       </c>
       <c r="V162" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W162" s="2" t="s">
         <v>38</v>
@@ -18440,7 +18437,7 @@
     </row>
     <row r="163" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>24</v>
@@ -18449,46 +18446,46 @@
         <v>5</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="N163" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O163" s="2" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="P163" s="2" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="Q163" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="R163" s="3" t="s">
         <v>35</v>
@@ -18503,7 +18500,7 @@
         <v>36</v>
       </c>
       <c r="V163" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W163" s="2" t="s">
         <v>38</v>
@@ -18511,7 +18508,7 @@
     </row>
     <row r="164" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>24</v>
@@ -18520,46 +18517,46 @@
         <v>5</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="N164" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O164" s="2" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="P164" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="Q164" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="R164" s="3" t="s">
         <v>35</v>
@@ -18574,7 +18571,7 @@
         <v>36</v>
       </c>
       <c r="V164" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W164" s="2" t="s">
         <v>290</v>
@@ -18582,7 +18579,7 @@
     </row>
     <row r="165" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>24</v>
@@ -18591,46 +18588,46 @@
         <v>5</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="G165" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="I165" s="2" t="s">
         <v>1346</v>
       </c>
-      <c r="H165" s="2" t="s">
-        <v>1344</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>1345</v>
-      </c>
       <c r="J165" s="11" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="N165" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O165" s="2" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="P165" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="Q165" s="2" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="R165" s="3" t="s">
         <v>35</v>
@@ -18645,7 +18642,7 @@
         <v>36</v>
       </c>
       <c r="V165" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W165" s="2" t="s">
         <v>38</v>
@@ -18653,7 +18650,7 @@
     </row>
     <row r="166" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>24</v>
@@ -18662,46 +18659,46 @@
         <v>5</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="N166" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O166" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="P166" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="Q166" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="R166" s="3" t="s">
         <v>35</v>
@@ -18716,7 +18713,7 @@
         <v>36</v>
       </c>
       <c r="V166" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W166" s="2" t="s">
         <v>290</v>
@@ -18724,7 +18721,7 @@
     </row>
     <row r="167" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>24</v>
@@ -18733,46 +18730,46 @@
         <v>5</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="J167" s="11" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="N167" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O167" s="2" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="P167" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="R167" s="3" t="s">
         <v>35</v>
@@ -18787,7 +18784,7 @@
         <v>36</v>
       </c>
       <c r="V167" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W167" s="2" t="s">
         <v>38</v>
@@ -18795,7 +18792,7 @@
     </row>
     <row r="168" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>24</v>
@@ -18804,46 +18801,46 @@
         <v>5</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="G168" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="H168" s="2" t="s">
         <v>1875</v>
       </c>
-      <c r="H168" s="2" t="s">
+      <c r="I168" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="J168" s="2" t="s">
         <v>1874</v>
-      </c>
-      <c r="I168" s="2" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J168" s="2" t="s">
-        <v>1873</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="N168" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O168" s="2" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="P168" s="2" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="Q168" s="2" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="R168" s="3" t="s">
         <v>35</v>
@@ -18858,7 +18855,7 @@
         <v>36</v>
       </c>
       <c r="V168" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W168" s="2" t="s">
         <v>38</v>
@@ -18866,7 +18863,7 @@
     </row>
     <row r="169" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>24</v>
@@ -18875,46 +18872,46 @@
         <v>5</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="N169" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O169" s="2" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="P169" s="2" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="Q169" s="2" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="R169" s="3" t="s">
         <v>35</v>
@@ -18929,7 +18926,7 @@
         <v>36</v>
       </c>
       <c r="V169" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W169" s="2" t="s">
         <v>38</v>
@@ -18937,7 +18934,7 @@
     </row>
     <row r="170" spans="1:23" ht="90" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>24</v>
@@ -18946,46 +18943,46 @@
         <v>5</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="G170" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H170" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="H170" s="2" t="s">
+      <c r="I170" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="J170" s="11" t="s">
         <v>1390</v>
-      </c>
-      <c r="I170" s="2" t="s">
-        <v>1878</v>
-      </c>
-      <c r="J170" s="11" t="s">
-        <v>1389</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="N170" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O170" s="2" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="Q170" s="2" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="R170" s="3" t="s">
         <v>35</v>
@@ -19000,7 +18997,7 @@
         <v>36</v>
       </c>
       <c r="V170" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W170" s="2" t="s">
         <v>38</v>
@@ -19008,7 +19005,7 @@
     </row>
     <row r="171" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>24</v>
@@ -19017,46 +19014,46 @@
         <v>5</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="N171" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O171" s="2" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="P171" s="2" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="Q171" s="2" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="R171" s="3" t="s">
         <v>35</v>
@@ -19071,7 +19068,7 @@
         <v>36</v>
       </c>
       <c r="V171" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W171" s="2" t="s">
         <v>38</v>
@@ -19079,7 +19076,7 @@
     </row>
     <row r="172" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>24</v>
@@ -19088,46 +19085,46 @@
         <v>5</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="G172" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="I172" s="2" t="s">
         <v>1409</v>
       </c>
-      <c r="H172" s="2" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I172" s="2" t="s">
-        <v>1408</v>
-      </c>
       <c r="J172" s="11" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="N172" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O172" s="2" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="Q172" s="2" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="R172" s="3" t="s">
         <v>35</v>
@@ -19142,7 +19139,7 @@
         <v>36</v>
       </c>
       <c r="V172" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W172" s="2" t="s">
         <v>290</v>
@@ -19150,7 +19147,7 @@
     </row>
     <row r="173" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>24</v>
@@ -19159,22 +19156,22 @@
         <v>5</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>381</v>
@@ -19183,22 +19180,22 @@
         <v>163</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="N173" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O173" s="2" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="P173" s="2" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="Q173" s="2" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="R173" s="3" t="s">
         <v>35</v>
@@ -19213,7 +19210,7 @@
         <v>36</v>
       </c>
       <c r="V173" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W173" s="2" t="s">
         <v>38</v>
@@ -19221,7 +19218,7 @@
     </row>
     <row r="174" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>24</v>
@@ -19230,13 +19227,13 @@
         <v>5</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>458</v>
@@ -19245,31 +19242,31 @@
         <v>459</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="J174" s="11" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="N174" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O174" s="2" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="Q174" s="2" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="R174" s="3" t="s">
         <v>35</v>
@@ -19284,7 +19281,7 @@
         <v>36</v>
       </c>
       <c r="V174" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W174" s="2" t="s">
         <v>38</v>
@@ -19292,7 +19289,7 @@
     </row>
     <row r="175" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>24</v>
@@ -19301,46 +19298,46 @@
         <v>5</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="J175" s="11" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="N175" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O175" s="2" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="P175" s="2" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="Q175" s="2" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="R175" s="3" t="s">
         <v>35</v>
@@ -19355,7 +19352,7 @@
         <v>36</v>
       </c>
       <c r="V175" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W175" s="2" t="s">
         <v>38</v>
@@ -19363,7 +19360,7 @@
     </row>
     <row r="176" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>24</v>
@@ -19372,46 +19369,46 @@
         <v>5</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="J176" s="11" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="N176" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O176" s="2" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="P176" s="2" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="Q176" s="2" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="R176" s="3" t="s">
         <v>35</v>
@@ -19426,7 +19423,7 @@
         <v>36</v>
       </c>
       <c r="V176" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W176" s="2" t="s">
         <v>38</v>
@@ -19434,7 +19431,7 @@
     </row>
     <row r="177" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>24</v>
@@ -19443,46 +19440,46 @@
         <v>5</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="N177" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O177" s="2" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="P177" s="2" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="Q177" s="2" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="R177" s="3" t="s">
         <v>35</v>
@@ -19497,7 +19494,7 @@
         <v>36</v>
       </c>
       <c r="V177" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W177" s="2" t="s">
         <v>290</v>
@@ -19505,7 +19502,7 @@
     </row>
     <row r="178" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>24</v>
@@ -19514,46 +19511,46 @@
         <v>5</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="H178" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J178" s="11" t="s">
         <v>1459</v>
-      </c>
-      <c r="I178" s="2" t="s">
-        <v>1460</v>
-      </c>
-      <c r="J178" s="11" t="s">
-        <v>1458</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="N178" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O178" s="2" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="P178" s="2" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="Q178" s="2" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="R178" s="3" t="s">
         <v>35</v>
@@ -19568,7 +19565,7 @@
         <v>36</v>
       </c>
       <c r="V178" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W178" s="2" t="s">
         <v>38</v>
@@ -19576,7 +19573,7 @@
     </row>
     <row r="179" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>24</v>
@@ -19585,46 +19582,46 @@
         <v>5</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="J179" s="11" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="N179" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O179" s="2" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="P179" s="2" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="Q179" s="2" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="R179" s="3" t="s">
         <v>35</v>
@@ -19639,7 +19636,7 @@
         <v>36</v>
       </c>
       <c r="V179" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W179" s="2" t="s">
         <v>38</v>
@@ -19647,7 +19644,7 @@
     </row>
     <row r="180" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>24</v>
@@ -19656,46 +19653,46 @@
         <v>5</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="J180" s="11" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="N180" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O180" s="2" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="P180" s="2" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="Q180" s="2" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="R180" s="3" t="s">
         <v>35</v>
@@ -19710,7 +19707,7 @@
         <v>36</v>
       </c>
       <c r="V180" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W180" s="2" t="s">
         <v>290</v>
@@ -19718,7 +19715,7 @@
     </row>
     <row r="181" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>24</v>
@@ -19727,46 +19724,46 @@
         <v>5</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="N181" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="P181" s="2" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="R181" s="3" t="s">
         <v>35</v>
@@ -19781,7 +19778,7 @@
         <v>36</v>
       </c>
       <c r="V181" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W181" s="2" t="s">
         <v>38</v>
@@ -19789,7 +19786,7 @@
     </row>
     <row r="182" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>24</v>
@@ -19798,46 +19795,46 @@
         <v>5</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="G182" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="I182" s="2" t="s">
         <v>1495</v>
       </c>
-      <c r="H182" s="2" t="s">
+      <c r="J182" s="11" t="s">
         <v>1902</v>
-      </c>
-      <c r="I182" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="J182" s="11" t="s">
-        <v>1901</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="N182" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O182" s="2" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="R182" s="3" t="s">
         <v>35</v>
@@ -19852,7 +19849,7 @@
         <v>36</v>
       </c>
       <c r="V182" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W182" s="2" t="s">
         <v>38</v>
@@ -19860,7 +19857,7 @@
     </row>
     <row r="183" spans="1:23" ht="120" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>24</v>
@@ -19869,46 +19866,46 @@
         <v>5</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H183" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="I183" s="2" t="s">
         <v>1504</v>
       </c>
-      <c r="I183" s="2" t="s">
-        <v>1503</v>
-      </c>
       <c r="J183" s="11" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L183" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="M183" s="2" t="s">
         <v>1906</v>
-      </c>
-      <c r="M183" s="2" t="s">
-        <v>1905</v>
       </c>
       <c r="N183" s="3" t="s">
         <v>294</v>
       </c>
       <c r="O183" s="2" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="P183" s="2" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="R183" s="3" t="s">
         <v>35</v>
@@ -19923,7 +19920,7 @@
         <v>36</v>
       </c>
       <c r="V183" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W183" s="2" t="s">
         <v>38</v>
@@ -19931,7 +19928,7 @@
     </row>
     <row r="184" spans="1:23" ht="30" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>24</v>
@@ -19940,16 +19937,16 @@
         <v>5</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>460</v>
@@ -19964,22 +19961,22 @@
         <v>163</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="N184" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O184" s="2" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="R184" s="3" t="s">
         <v>35</v>
@@ -19994,7 +19991,7 @@
         <v>36</v>
       </c>
       <c r="V184" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W184" s="2" t="s">
         <v>38</v>
@@ -20002,7 +19999,7 @@
     </row>
     <row r="185" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>24</v>
@@ -20011,46 +20008,46 @@
         <v>5</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="N185" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="P185" s="2" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="Q185" s="2" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="R185" s="3" t="s">
         <v>35</v>
@@ -20065,7 +20062,7 @@
         <v>36</v>
       </c>
       <c r="V185" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W185" s="2" t="s">
         <v>290</v>
@@ -20073,7 +20070,7 @@
     </row>
     <row r="186" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>24</v>
@@ -20082,34 +20079,34 @@
         <v>5</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>163</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="N186" s="3" t="s">
         <v>47</v>
@@ -20118,10 +20115,10 @@
         <v>339</v>
       </c>
       <c r="P186" s="2" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="Q186" s="2" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="R186" s="3" t="s">
         <v>35</v>
@@ -20136,7 +20133,7 @@
         <v>36</v>
       </c>
       <c r="V186" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W186" s="2" t="s">
         <v>38</v>
@@ -20144,7 +20141,7 @@
     </row>
     <row r="187" spans="1:23" ht="60" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>24</v>
@@ -20153,46 +20150,46 @@
         <v>5</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="G187" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="I187" s="2" t="s">
         <v>1537</v>
       </c>
-      <c r="H187" s="2" t="s">
+      <c r="J187" s="11" t="s">
         <v>1535</v>
-      </c>
-      <c r="I187" s="2" t="s">
-        <v>1536</v>
-      </c>
-      <c r="J187" s="11" t="s">
-        <v>1534</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="N187" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O187" s="2" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="P187" s="2" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="R187" s="3" t="s">
         <v>35</v>
@@ -20207,7 +20204,7 @@
         <v>36</v>
       </c>
       <c r="V187" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W187" s="2" t="s">
         <v>38</v>
@@ -20215,7 +20212,7 @@
     </row>
     <row r="188" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>24</v>
@@ -20224,46 +20221,46 @@
         <v>5</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="J188" s="11" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="N188" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O188" s="2" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="P188" s="2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="Q188" s="2" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="R188" s="3" t="s">
         <v>35</v>
@@ -20278,7 +20275,7 @@
         <v>36</v>
       </c>
       <c r="V188" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W188" s="2" t="s">
         <v>38</v>
@@ -20286,7 +20283,7 @@
     </row>
     <row r="189" spans="1:23" ht="45" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>24</v>
@@ -20295,46 +20292,46 @@
         <v>5</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="N189" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O189" s="2" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="P189" s="2" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="Q189" s="2" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="R189" s="3" t="s">
         <v>35</v>
@@ -20349,7 +20346,7 @@
         <v>36</v>
       </c>
       <c r="V189" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W189" s="2" t="s">
         <v>290</v>
@@ -20357,7 +20354,7 @@
     </row>
     <row r="190" spans="1:23" ht="75" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>24</v>
@@ -20366,46 +20363,46 @@
         <v>5</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H190" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="J190" s="2" t="s">
         <v>1565</v>
-      </c>
-      <c r="I190" s="2" t="s">
-        <v>1563</v>
-      </c>
-      <c r="J190" s="2" t="s">
-        <v>1564</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="N190" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O190" s="2" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="P190" s="2" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="Q190" s="2" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="R190" s="3" t="s">
         <v>35</v>
@@ -20420,7 +20417,7 @@
         <v>36</v>
       </c>
       <c r="V190" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="W190" s="2" t="s">
         <v>290</v>
@@ -20446,12 +20443,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21.6" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.35">
@@ -20459,12 +20456,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B5" s="8">
         <v>37</v>
@@ -20472,7 +20469,7 @@
     </row>
     <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B6" s="8">
         <v>46</v>
@@ -20480,7 +20477,7 @@
     </row>
     <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B7" s="8">
         <v>30</v>
@@ -20488,7 +20485,7 @@
     </row>
     <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B8" s="8">
         <v>47</v>
@@ -20496,7 +20493,7 @@
     </row>
     <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B9" s="8">
         <v>31</v>
@@ -20504,7 +20501,7 @@
     </row>
     <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B10" s="7">
         <v>191</v>
@@ -20512,15 +20509,15 @@
     </row>
     <row r="13" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.35">
@@ -20528,7 +20525,7 @@
         <v>0</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.35">
@@ -20536,15 +20533,15 @@
         <v>1</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="60" x14ac:dyDescent="0.35">
@@ -20552,7 +20549,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.35">
@@ -20560,15 +20557,15 @@
         <v>5</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.35">
@@ -20576,7 +20573,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.35">
@@ -20584,7 +20581,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="60" x14ac:dyDescent="0.35">
@@ -20592,7 +20589,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="75" x14ac:dyDescent="0.35">
@@ -20600,23 +20597,23 @@
         <v>13</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.35">
@@ -20624,7 +20621,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.35">
@@ -20632,7 +20629,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.35">
@@ -20640,12 +20637,12 @@
         <v>22</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="18" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B32" s="18"/>
     </row>
